--- a/ledger/patents.xlsx
+++ b/ledger/patents.xlsx
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -707,7 +707,7 @@
     <col width="48" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
@@ -3621,11 +3621,7 @@
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>证据复核 r2：权利要求与摘要</t>
-        </is>
-      </c>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr">
         <is>
           <t>evidence-review-r2</t>
@@ -4634,11 +4630,7 @@
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>证据复核 r2：权利要求与摘要</t>
-        </is>
-      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr">
         <is>
           <t>evidence-review-r2</t>
@@ -4764,11 +4756,7 @@
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>证据复核 r2：权利要求与摘要</t>
-        </is>
-      </c>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr">
         <is>
           <t>evidence-review-r2</t>
@@ -5526,11 +5514,7 @@
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>证据复核 r2：权利要求与摘要</t>
-        </is>
-      </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr">
         <is>
           <t>evidence-review-r2</t>
@@ -5656,11 +5640,7 @@
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>证据复核 r2：权利要求与摘要</t>
-        </is>
-      </c>
+      <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr">
         <is>
           <t>evidence-review-r2</t>
@@ -7427,7 +7407,7 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>证据复核 r2：权利要求与摘要</t>
+          <t>Gate③ 证据复核：权利要求级阅读（EPI 四件）</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -7557,7 +7537,7 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>证据复核 r2：权利要求与摘要</t>
+          <t>Gate③ 证据复核：权利要求级阅读（EPI 四件）</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -8949,7 +8929,7 @@
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>证据复核 r2：权利要求与摘要</t>
+          <t>Gate③ 证据复核：权利要求级阅读（EPI 四件）</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -15923,7 +15903,7 @@
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>证据复核 r2：权利要求与摘要</t>
+          <t>Gate③ 证据复核：权利要求级阅读（EPI 四件）</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">

--- a/ledger/patents.xlsx
+++ b/ledger/patents.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
@@ -660,10 +660,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>counts.unique_publication_ids</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Empty months ≠ zero hits. 2025-09 paused. No zero-omission claim.</t>
         </is>
@@ -680,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD120"/>
+  <dimension ref="A1:AL120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -705,14 +715,22 @@
     <col width="48" customWidth="1" min="20" max="20"/>
     <col width="26" customWidth="1" min="21" max="21"/>
     <col width="48" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="48" customWidth="1" min="24" max="24"/>
+    <col width="48" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="19" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="23" customWidth="1" min="31" max="31"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="48" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="27" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="44" customWidth="1" min="37" max="37"/>
+    <col width="48" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,6 +882,46 @@
       <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>discovery_source</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>team_independent_read</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>read_disposition</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>read_status</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pending_reason</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>failure_or_pending_reason</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>read_query</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>official_source_url</t>
         </is>
       </c>
     </row>
@@ -992,6 +1050,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1119,6 +1185,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1245,6 +1319,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1372,6 +1454,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1498,6 +1588,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1624,6 +1722,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1746,6 +1852,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1872,6 +1986,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1998,6 +2120,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2125,6 +2255,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2252,6 +2390,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2379,6 +2525,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2505,6 +2659,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2631,6 +2793,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2757,6 +2927,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2883,6 +3061,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3010,6 +3196,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3136,6 +3330,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3262,6 +3464,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3388,6 +3598,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3515,6 +3733,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3622,16 +3848,8 @@
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>evidence-review-r2</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
@@ -3641,6 +3859,24 @@
           <t>independent_search</t>
         </is>
       </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>included_not_team_read</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Preclean 同族台湾公开；未计 team_read。</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3767,6 +4003,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3893,6 +4137,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4019,6 +4271,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4145,6 +4405,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4271,6 +4539,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4397,6 +4673,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4524,6 +4808,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4631,16 +4923,8 @@
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>evidence-review-r2</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
@@ -4650,6 +4934,24 @@
           <t>independent_search</t>
         </is>
       </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>included_not_team_read</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>独立纳入；HBT/SiGe 界面与选择性外延边界；未计 team_read。</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4757,16 +5059,8 @@
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>evidence-review-r2</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
@@ -4776,6 +5070,24 @@
           <t>independent_search</t>
         </is>
       </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>included_not_team_read</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>未计团队已读：授权全文未在本轮固化 sha256/阅读跨度。</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4902,6 +5214,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5028,6 +5348,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5154,6 +5482,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5281,6 +5617,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5408,6 +5752,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5515,16 +5867,8 @@
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>evidence-review-r2</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
@@ -5534,6 +5878,24 @@
           <t>independent_search</t>
         </is>
       </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>included_not_team_read</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>独立纳入；外延层形成方法；未计 team_read。</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5641,16 +6003,8 @@
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>evidence-review-r2</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
@@ -5660,6 +6014,24 @@
           <t>independent_search</t>
         </is>
       </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>included_not_team_read</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Preclean 独立纳入；FAM-merge-hybrid-preclean；未计 team_read。</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5786,6 +6158,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5912,6 +6292,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6038,6 +6426,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6164,6 +6560,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6290,6 +6694,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6416,6 +6828,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6543,6 +6963,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6669,6 +7097,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6795,6 +7231,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6921,6 +7365,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7047,6 +7499,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7173,6 +7633,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7299,6 +7767,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7400,19 +7876,27 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260071979A1/en</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
+          <t>https://patents.google.com/patent/US20260071979A1/en | https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260071979</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>2026-10-20T10:03:49Z</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2ee8d4206cf3f1b4a700bced605d01fe4b613382b7ba4fd6f7dbccb6d7579c2c</t>
+        </is>
+      </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>Gate③ 证据复核：权利要求级阅读（EPI 四件）</t>
+          <t>USPTO 公开 PDF：独立权利要求 1 与方法步骤; 权利要求中 XRF / superlattice 相关从属项</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>epi-evidence-review-r2</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7429,6 +7913,28 @@
           <t>independent_search</t>
         </is>
       </c>
+      <c r="AE53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>team_read_claims_level</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>独立 EPI 检索 Gate③ r2；Si/SiGe 超晶格 + XRF 工艺控制。</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260071979</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7533,16 +8039,20 @@
           <t>https://patents.google.com/patent/CN121693111A/en</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>2026-10-20T10:05:00Z</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Gate③ 证据复核：权利要求级阅读（EPI 四件）</t>
+          <t>公开文本权利要求 1–5（Google Patents 页面；无 PDF sha256）; 摘要：电学监测外延层厚度与测试结构</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>epi-evidence-review-r2</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7557,6 +8067,28 @@
       <c r="AD54" t="inlineStr">
         <is>
           <t>independent_search</t>
+        </is>
+      </c>
+      <c r="AE54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>team_read_claims_level</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>独立 EPI 检索 Gate③ r2；外延层厚度电学监测。</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>https://patents.google.com/patent/CN121693111A/en</t>
         </is>
       </c>
     </row>
@@ -7685,6 +8217,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7811,6 +8351,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7937,6 +8485,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8063,6 +8619,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8189,6 +8753,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8315,6 +8887,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8441,6 +9021,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8567,6 +9155,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8694,6 +9290,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8821,6 +9425,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8922,19 +9534,27 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260055532A1/en</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
+          <t>https://patents.google.com/patent/US20260055532A1/en | https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260055532</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>2026-10-20T10:03:49Z</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>42e816969db0d2d7402244b373944637ec21cb91bc3410bb8764b1783caaa7c6</t>
+        </is>
+      </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Gate③ 证据复核：权利要求级阅读（EPI 四件）</t>
+          <t>USPTO 公开 PDF：独立权利要求 1 及与边缘区域工艺相关的从属项; 摘要中对 edge defect / substrate edge 的表述</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>epi-evidence-review-r2</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8949,6 +9569,28 @@
       <c r="AD65" t="inlineStr">
         <is>
           <t>independent_search</t>
+        </is>
+      </c>
+      <c r="AE65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>team_read_claims_level</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>独立 EPI 检索 Gate③ r2；晶圆边缘膜缺陷与外延制程腔体。</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260055532</t>
         </is>
       </c>
     </row>
@@ -9077,6 +9719,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9203,6 +9853,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9329,6 +9987,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9455,6 +10121,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9582,6 +10256,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9709,6 +10391,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9835,6 +10525,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9962,6 +10660,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10089,6 +10795,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10215,6 +10929,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10341,6 +11063,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10467,6 +11197,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10593,6 +11331,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10719,6 +11465,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10845,6 +11599,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10972,6 +11734,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -11098,6 +11868,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -11225,6 +12003,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11352,6 +12138,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -11481,6 +12275,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11608,6 +12410,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11737,6 +12547,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11864,6 +12682,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11991,6 +12817,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -12118,6 +12952,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -12245,6 +13087,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -12372,6 +13222,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr"/>
+      <c r="AL92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -12498,6 +13356,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12621,6 +13487,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr"/>
+      <c r="AL94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12748,6 +13622,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr"/>
+      <c r="AL95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12874,6 +13756,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13001,6 +13891,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -13128,6 +14026,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -13255,6 +14161,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -13384,6 +14298,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13511,6 +14433,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13634,6 +14564,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13763,6 +14701,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13890,6 +14836,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -14017,6 +14971,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -14144,6 +15106,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -14271,6 +15241,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -14398,6 +15376,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -14525,6 +15511,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14652,6 +15646,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="inlineStr"/>
+      <c r="AK110" t="inlineStr"/>
+      <c r="AL110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -14779,6 +15781,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE111" t="inlineStr"/>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
+      <c r="AJ111" t="inlineStr"/>
+      <c r="AK111" t="inlineStr"/>
+      <c r="AL111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14906,6 +15916,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr"/>
+      <c r="AL112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -15033,6 +16051,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE113" t="inlineStr"/>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr"/>
+      <c r="AK113" t="inlineStr"/>
+      <c r="AL113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -15160,6 +16186,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr"/>
+      <c r="AK114" t="inlineStr"/>
+      <c r="AL114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -15287,6 +16321,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="inlineStr"/>
+      <c r="AK115" t="inlineStr"/>
+      <c r="AL115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -15414,6 +16456,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="inlineStr"/>
+      <c r="AK116" t="inlineStr"/>
+      <c r="AL116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -15541,6 +16591,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr"/>
+      <c r="AJ117" t="inlineStr"/>
+      <c r="AK117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -15668,6 +16726,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr"/>
+      <c r="AK118" t="inlineStr"/>
+      <c r="AL118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -15795,6 +16861,14 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr"/>
+      <c r="AK119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -15896,19 +16970,27 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250327209A1/en</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
+          <t>https://patents.google.com/patent/US20250327209A1/en | https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20250327209</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>2026-10-20T10:03:49Z</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>04d83748266705e79395aab59ed1387487518cdf71a91fd5ab6db77e0ad59c69</t>
+        </is>
+      </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>Gate③ 证据复核：权利要求级阅读（EPI 四件）</t>
+          <t>USPTO 公开 PDF（sha256 见 source_sha256）：独立权利要求 1–3 与方法/反应器主题; 摘要与实施方式中与腔体、气体路径、基座相关的段落（目视复核）</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>epi-evidence-review-r2</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15923,6 +17005,28 @@
       <c r="AD120" t="inlineStr">
         <is>
           <t>independent_search</t>
+        </is>
+      </c>
+      <c r="AE120" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>team_read_claims_level</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="inlineStr"/>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>独立 EPI 检索 Gate③ r2；纳入边界=Si 外延沉积反应器/工艺。</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20250327209</t>
         </is>
       </c>
     </row>
@@ -15937,7 +17041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16976,12 +18080,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WO2026096517A1</t>
+          <t>TW202628839A</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -16991,39 +18095,39 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026096517A1/en</t>
+          <t>https://patents.google.com/patent/TW202628839A/en</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PCT/US2025/052926</t>
+          <t>TW114142104A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TW202628839A</t>
+          <t>US20260152871A1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FAM-merge-hybrid-preclean</t>
+          <t>89380832</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TW202628839A</t>
+          <t>US20260152871A1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -17033,12 +18137,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/TW202628839A/en</t>
+          <t>https://patents.google.com/patent/US20260152871A1/en</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>TW114142104A</t>
+          <t>US18/880,180</t>
         </is>
       </c>
     </row>
@@ -17050,37 +18154,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>US20260152871A1</t>
+          <t>US12652840B2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>89380832</t>
+          <t>84977174</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>US20260152871A1</t>
+          <t>US12652840B2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260152871A1/en</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12652840</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>US18/880,180</t>
+          <t>US17/870,327</t>
         </is>
       </c>
     </row>
@@ -17092,22 +18196,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US12652840B2</t>
+          <t>US12655537B2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>84977174</t>
+          <t>US12655537B2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>US12652840B2</t>
+          <t>US12655537B2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -17117,12 +18221,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12652840</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12655537</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>US17/870,327</t>
+          <t>US18/861,658</t>
         </is>
       </c>
     </row>
@@ -17134,17 +18238,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>US12655537B2</t>
+          <t>US12660266B2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US12655537B2</t>
+          <t>90244475</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>US12655537B2</t>
+          <t>US12660266B2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17159,12 +18263,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12655537</t>
+          <t>https://patents.google.com/patent/US12660266B2/en</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>US18/861,658</t>
+          <t>US18/128,051</t>
         </is>
       </c>
     </row>
@@ -17176,22 +18280,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US12660266B2</t>
+          <t>JP7882130B2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>90244475</t>
+          <t>92423958</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>US12660266B2</t>
+          <t>JP7882130B2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -17201,12 +18305,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12660266B2/en</t>
+          <t>https://patents.google.com/patent/JP7882130B2/en</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>US18/128,051</t>
+          <t>JP2023016773A</t>
         </is>
       </c>
     </row>
@@ -17218,17 +18322,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JP7882130B2</t>
+          <t>US12672330B2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>92423958</t>
+          <t>88790981</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JP7882130B2</t>
+          <t>US12672330B2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17243,12 +18347,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP7882130B2/en</t>
+          <t>https://patents.google.com/patent/US12672330B2/en</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>JP2023016773A</t>
+          <t>US18/181,173</t>
         </is>
       </c>
     </row>
@@ -17260,37 +18364,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>US12672330B2</t>
+          <t>US20260164725A1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>88790981</t>
+          <t>77370546</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>US12672330B2</t>
+          <t>US20260164725A1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12672330B2/en</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260164725</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>US18/181,173</t>
+          <t>US19/179,534</t>
         </is>
       </c>
     </row>
@@ -17302,22 +18406,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>US20260164725A1</t>
+          <t>CN122294515A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>77370546</t>
+          <t>CN122294515A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>US20260164725A1</t>
+          <t>CN122294515A</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -17327,12 +18431,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260164725</t>
+          <t>https://patents.google.com/patent/CN122294515A/en</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>US19/179,534</t>
+          <t>CN202610446224.8A</t>
         </is>
       </c>
     </row>
@@ -17344,64 +18448,64 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CN122294515A</t>
+          <t>US12660522B2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CN122294515A</t>
+          <t>US12660522B2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CN122294515A</t>
+          <t>US12660522B2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN122294515A/en</t>
+          <t>https://patents.google.com/patent/US12660522B2/en</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CN202610446224.8A</t>
+          <t>US17/615,877</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>US12660522B2</t>
+          <t>US12628600B2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US12660522B2</t>
+          <t>89510362</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>US12660522B2</t>
+          <t>US12628600B2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -17411,12 +18515,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12660522B2/en</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12628600</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>US17/615,877</t>
+          <t>US18/074,306</t>
         </is>
       </c>
     </row>
@@ -17428,37 +18532,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US12628600B2</t>
+          <t>US20260136521A1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>89510362</t>
+          <t>84891093</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>US12628600B2</t>
+          <t>US20260136521A1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12628600</t>
+          <t>https://patents.google.com/patent/US20260136521A1/en</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>US18/074,306</t>
+          <t>US19/438,155</t>
         </is>
       </c>
     </row>
@@ -17470,37 +18574,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>US20260136521A1</t>
+          <t>US20260143977A1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>84891093</t>
+          <t>US20260143977A1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>US20260136521A1</t>
+          <t>US12635427B2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260136521A1/en</t>
+          <t>https://patents.google.com/patent/US12635427B2/en</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>US19/438,155</t>
+          <t>US18/103,886</t>
         </is>
       </c>
     </row>
@@ -17522,27 +18626,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>US12635427B2</t>
+          <t>US20260143977A1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12635427B2/en</t>
+          <t>https://patents.google.com/patent/US20260143977A1/en</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>US18/103,886</t>
+          <t>US19/451,584</t>
         </is>
       </c>
     </row>
@@ -17554,22 +18658,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US20260143977A1</t>
+          <t>WO2026101868A1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US20260143977A1</t>
+          <t>99765971</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>US20260143977A1</t>
+          <t>WO2026101868A1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -17579,12 +18683,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260143977A1/en</t>
+          <t>https://patents.google.com/patent/WO2026101868A1/en</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>US19/451,584</t>
+          <t>PCT/US2025/053886</t>
         </is>
       </c>
     </row>
@@ -17606,12 +18710,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>WO2026101868A1</t>
+          <t>TW202621247A</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -17621,12 +18725,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026101868A1/en</t>
+          <t>https://tiponet.tipo.gov.tw/twpat1/twpatc/twpatkm?!!FRURL202621247</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PCT/US2025/053886</t>
+          <t>TW114136994</t>
         </is>
       </c>
     </row>
@@ -17638,22 +18742,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WO2026101868A1</t>
+          <t>US20260150594A1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>99765971</t>
+          <t>98931074</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TW202621247A</t>
+          <t>US20260150594A1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -17663,12 +18767,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://tiponet.tipo.gov.tw/twpat1/twpatc/twpatkm?!!FRURL202621247</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260150594</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>TW114136994</t>
+          <t>US19/312,739</t>
         </is>
       </c>
     </row>
@@ -17680,22 +18784,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>US20260150594A1</t>
+          <t>CN122069948A</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>98931074</t>
+          <t>CN122069948A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>US20260150594A1</t>
+          <t>CN122069948A</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -17705,12 +18809,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260150594</t>
+          <t>https://patents.google.com/patent/CN122069948A/en</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>US19/312,739</t>
+          <t>CN202610121551.6A</t>
         </is>
       </c>
     </row>
@@ -17722,22 +18826,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CN122069948A</t>
+          <t>WO2026096517A1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CN122069948A</t>
+          <t>FAM-merge-hybrid-preclean</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CN122069948A</t>
+          <t>WO2026096517A1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -17747,39 +18851,39 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN122069948A/en</t>
+          <t>https://patents.google.com/patent/WO2026096517A1/en</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CN202610121551.6A</t>
+          <t>PCT/US2025/052926</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WO2026096517A1</t>
+          <t>US20260092399A1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FAM-merge-hybrid-preclean</t>
+          <t>US20260092399A1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>WO2026096517A1</t>
+          <t>US20260092399A1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -17789,39 +18893,39 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026096517A1/en</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260092399</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>PCT/US2025/052926</t>
+          <t>US19/342,449</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WO2026096517A1</t>
+          <t>JP2026512448A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FAM-merge-hybrid-preclean</t>
+          <t>94372436</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TW202628839A</t>
+          <t>JP2026512448A</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -17831,12 +18935,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/TW202628839A/en</t>
+          <t>https://patents.google.com/patent/JP2026512448A/en</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>TW114142104A</t>
+          <t>JP2025-558685</t>
         </is>
       </c>
     </row>
@@ -17848,37 +18952,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>US20260092399A1</t>
+          <t>KR102954223B1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US20260092399A1</t>
+          <t>85153853</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>US20260092399A1</t>
+          <t>KR102954223B1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260092399</t>
+          <t>https://patents.google.com/patent/KR102954223B1/en</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>US19/342,449</t>
+          <t>KR10-2024-7002370</t>
         </is>
       </c>
     </row>
@@ -17890,17 +18994,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JP2026512448A</t>
+          <t>WO2026079031A1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>94372436</t>
+          <t>99438786</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>JP2026512448A</t>
+          <t>WO2026079031A1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -17915,12 +19019,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP2026512448A/en</t>
+          <t>https://patents.google.com/patent/WO2026079031A1/en</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>JP2025-558685</t>
+          <t>PCT/JP2025/031413</t>
         </is>
       </c>
     </row>
@@ -17932,37 +19036,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KR102954223B1</t>
+          <t>WO2026079031A1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>85153853</t>
+          <t>99438786</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KR102954223B1</t>
+          <t>JP2026068628A</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR102954223B1/en</t>
+          <t>https://patents.google.com/patent/JP2026068628A/en</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KR10-2024-7002370</t>
+          <t>JP2024-178436</t>
         </is>
       </c>
     </row>
@@ -17974,17 +19078,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WO2026079031A1</t>
+          <t>WO2026084898A1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>99438786</t>
+          <t>99436736</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>WO2026079031A1</t>
+          <t>US20260107704A1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -17999,12 +19103,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026079031A1/en</t>
+          <t>https://patents.google.com/patent/US20260107704A1/en</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>PCT/JP2025/031413</t>
+          <t>US18/960,281</t>
         </is>
       </c>
     </row>
@@ -18016,22 +19120,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WO2026079031A1</t>
+          <t>WO2026084898A1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>99438786</t>
+          <t>99436736</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JP2026068628A</t>
+          <t>WO2026084898A1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -18041,12 +19145,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP2026068628A/en</t>
+          <t>https://patents.google.com/patent/WO2026084898A1/en</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>JP2024-178436</t>
+          <t>PCT/US2025/049619</t>
         </is>
       </c>
     </row>
@@ -18058,22 +19162,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WO2026084898A1</t>
+          <t>US20260123349A1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>99436736</t>
+          <t>99550322</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>US20260107704A1</t>
+          <t>US20260123349A1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -18083,12 +19187,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260107704A1/en</t>
+          <t>https://patents.google.com/patent/US20260123349A1/en</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>US18/960,281</t>
+          <t>US18/932,875</t>
         </is>
       </c>
     </row>
@@ -18100,64 +19204,64 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WO2026084898A1</t>
+          <t>US12595587B2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>99436736</t>
+          <t>89498866</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>WO2026084898A1</t>
+          <t>US12595587B2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026084898A1/en</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12595587</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>PCT/US2025/049619</t>
+          <t>US18/350,517</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US20260123349A1</t>
+          <t>US20260068564A1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>99550322</t>
+          <t>98900333</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>US20260123349A1</t>
+          <t>US20260068564A1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -18167,56 +19271,52 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260123349A1/en</t>
+          <t>https://patents.google.com/patent/US20260068564A1/en</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>US18/932,875</t>
+          <t>US19/313,318</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>US12595587B2</t>
+          <t>US20260068564A1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>89498866</t>
+          <t>98900333</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>US12595587B2</t>
+          <t>WO2026055048A1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12595587</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>US18/350,517</t>
-        </is>
-      </c>
+          <t>https://patents.google.com/patent/WO2026055048A1/en</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -18226,22 +19326,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>US20260068564A1</t>
+          <t>US20260076125A1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>98900333</t>
+          <t>87518802</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>US20260068564A1</t>
+          <t>US20260076125A1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -18251,12 +19351,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260068564A1/en</t>
+          <t>https://patents.google.com/patent/US20260076125A1/en</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>US19/313,318</t>
+          <t>US19/394,353</t>
         </is>
       </c>
     </row>
@@ -18268,22 +19368,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>US20260068564A1</t>
+          <t>WO2026055216A1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>98900333</t>
+          <t>98901115</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>WO2026055048A1</t>
+          <t>US20260066234A1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -18293,7 +19393,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026055048A1/en</t>
+          <t>https://patents.google.com/patent/US20260066234A1/en</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -18306,17 +19406,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>US20260076125A1</t>
+          <t>WO2026055216A1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>87518802</t>
+          <t>98901115</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>US20260076125A1</t>
+          <t>WO2026055216A1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -18331,12 +19431,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260076125A1/en</t>
+          <t>https://patents.google.com/patent/WO2026055216A1/en</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>US19/394,353</t>
+          <t>PCT/US2025/044643</t>
         </is>
       </c>
     </row>
@@ -18348,22 +19448,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WO2026055216A1</t>
+          <t>KR20260039926A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>98901115</t>
+          <t>94372436</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>US20260066234A1</t>
+          <t>KR20260039926A</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -18373,10 +19473,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260066234A1/en</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>https://patents.google.com/patent/KR20260039926A/en</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>KR10-2025-7033751</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -18386,22 +19490,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WO2026055216A1</t>
+          <t>US20260090293A1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>98901115</t>
+          <t>90455087</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>WO2026055216A1</t>
+          <t>US20260090293A1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -18411,12 +19515,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026055216A1/en</t>
+          <t>https://patents.google.com/patent/US20260090293A1/en</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>PCT/US2025/044643</t>
+          <t>US19/114,262</t>
         </is>
       </c>
     </row>
@@ -18428,22 +19532,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KR20260039926A</t>
+          <t>JP2026510085A</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>94372436</t>
+          <t>90831515</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KR20260039926A</t>
+          <t>JP2026510085A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -18453,12 +19557,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR20260039926A/en</t>
+          <t>https://patents.google.com/patent/JP2026510085A/en</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>KR10-2025-7033751</t>
+          <t>JP2025-522844</t>
         </is>
       </c>
     </row>
@@ -18470,22 +19574,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>US20260090293A1</t>
+          <t>US20260071979A1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>90455087</t>
+          <t>US20260071979A1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>US20260090293A1</t>
+          <t>US20260071979A1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -18495,12 +19599,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260090293A1/en</t>
+          <t>https://patents.google.com/patent/US20260071979A1/en</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>US19/114,262</t>
+          <t>US19/321,663</t>
         </is>
       </c>
     </row>
@@ -18512,22 +19616,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JP2026510085A</t>
+          <t>CN121693111A</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>90831515</t>
+          <t>CN121693111A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JP2026510085A</t>
+          <t>CN121693111A</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -18537,81 +19641,81 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP2026510085A/en</t>
+          <t>https://patents.google.com/patent/CN121693111A/en</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>JP2025-522844</t>
+          <t>CN202511931241.2A</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>US20260071979A1</t>
+          <t>US12540400B2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US20260071979A1</t>
+          <t>95562156</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>US20260071979A1</t>
+          <t>US12540400B2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260071979A1/en</t>
+          <t>https://patents.google.com/patent/US12540400B2/en</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>US19/321,663</t>
+          <t>US18/500,690</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CN121693111A</t>
+          <t>US20260043170A1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CN121693111A</t>
+          <t>98698458</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CN121693111A</t>
+          <t>US20260043170A1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -18621,12 +19725,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN121693111A/en</t>
+          <t>https://patents.google.com/patent/US20260043170A1/en</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CN202511931241.2A</t>
+          <t>US19/245,121</t>
         </is>
       </c>
     </row>
@@ -18638,37 +19742,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>US12540400B2</t>
+          <t>US20260043170A1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>95562156</t>
+          <t>98698458</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>US12540400B2</t>
+          <t>WO2026039101A1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12540400B2/en</t>
+          <t>https://patents.google.com/patent/WO2026039101A1/en</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>US18/500,690</t>
+          <t>PCT/US2025/034435</t>
         </is>
       </c>
     </row>
@@ -18680,17 +19784,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>US20260043170A1</t>
+          <t>US20260047358A1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>98698458</t>
+          <t>98698156</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>US20260043170A1</t>
+          <t>US20260047358A1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -18705,12 +19809,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260043170A1/en</t>
+          <t>https://patents.google.com/patent/US20260047358A1/en</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>US19/245,121</t>
+          <t>US19/291,441</t>
         </is>
       </c>
     </row>
@@ -18722,22 +19826,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>US20260043170A1</t>
+          <t>US20260047358A1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>98698458</t>
+          <t>98698156</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>WO2026039101A1</t>
+          <t>WO2026035758A1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -18747,12 +19851,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026039101A1/en</t>
+          <t>https://patents.google.com/patent/WO2026035758A1/en</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>PCT/US2025/034435</t>
+          <t>PCT/US2025/040760</t>
         </is>
       </c>
     </row>
@@ -18764,22 +19868,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>US20260047358A1</t>
+          <t>WO2026035639A1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>98698156</t>
+          <t>98653272</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>US20260047358A1</t>
+          <t>US20260040668A1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -18789,12 +19893,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260047358A1/en</t>
+          <t>https://patents.google.com/patent/US20260040668A1/en</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>US19/291,441</t>
+          <t>US19/290,106</t>
         </is>
       </c>
     </row>
@@ -18806,22 +19910,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>US20260047358A1</t>
+          <t>WO2026035639A1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>98698156</t>
+          <t>98653272</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>WO2026035758A1</t>
+          <t>US20260040669A1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -18831,12 +19935,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026035758A1/en</t>
+          <t>https://patents.google.com/patent/US20260040669A1/en</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>PCT/US2025/040760</t>
+          <t>US19/290,149</t>
         </is>
       </c>
     </row>
@@ -18858,12 +19962,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>US20260040668A1</t>
+          <t>WO2026035639A1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -18873,12 +19977,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260040668A1/en</t>
+          <t>https://patents.google.com/patent/WO2026035639A1/en</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>US19/290,106</t>
+          <t>PCT/US2025/040558</t>
         </is>
       </c>
     </row>
@@ -18900,12 +20004,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>US20260040669A1</t>
+          <t>WO2026035645A1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -18915,12 +20019,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260040669A1/en</t>
+          <t>https://patents.google.com/patent/WO2026035645A1/en</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>US19/290,149</t>
+          <t>PCT/US2025/040571</t>
         </is>
       </c>
     </row>
@@ -18932,22 +20036,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WO2026035639A1</t>
+          <t>CN121519154A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>98653272</t>
+          <t>98706890</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>WO2026035639A1</t>
+          <t>CN121519154A</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -18957,12 +20061,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026035639A1/en</t>
+          <t>https://patents.google.com/patent/CN121519154A/en</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>PCT/US2025/040558</t>
+          <t>CN202411077362.0</t>
         </is>
       </c>
     </row>
@@ -18974,37 +20078,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WO2026035639A1</t>
+          <t>US12557185B2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>98653272</t>
+          <t>89664204</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>WO2026035645A1</t>
+          <t>US12557185B2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026035645A1/en</t>
+          <t>https://patents.google.com/patent/US12557185B2/en</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>PCT/US2025/040571</t>
+          <t>US17/875,036</t>
         </is>
       </c>
     </row>
@@ -19016,22 +20120,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CN121519154A</t>
+          <t>US20260049767A1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>98706890</t>
+          <t>98776697</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CN121519154A</t>
+          <t>US20260049767A1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -19041,12 +20145,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN121519154A/en</t>
+          <t>https://patents.google.com/patent/US20260049767A1/en</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CN202411077362.0</t>
+          <t>US18/812,711</t>
         </is>
       </c>
     </row>
@@ -19058,22 +20162,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>US12557185B2</t>
+          <t>US12564001B2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>89664204</t>
+          <t>83284110</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>US12557185B2</t>
+          <t>US12564001B2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -19083,12 +20187,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12557185B2/en</t>
+          <t>https://patents.google.com/patent/US12564001B2/en</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>US17/875,036</t>
+          <t>US17/697,145</t>
         </is>
       </c>
     </row>
@@ -19100,37 +20204,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>US20260049767A1</t>
+          <t>US12543516B2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>98776697</t>
+          <t>priority-US63-305926</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>US20260049767A1</t>
+          <t>US12543516B2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260049767A1/en</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12543516</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>US18/812,711</t>
+          <t>US18/161,681</t>
         </is>
       </c>
     </row>
@@ -19142,37 +20246,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>US12564001B2</t>
+          <t>US20260035835A1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>83284110</t>
+          <t>98611688</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>US12564001B2</t>
+          <t>US20260035835A1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12564001B2/en</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260035835</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>US17/697,145</t>
+          <t>US19/281,879</t>
         </is>
       </c>
     </row>
@@ -19184,64 +20288,64 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>US12543516B2</t>
+          <t>US20260055532A1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>priority-US63-305926</t>
+          <t>US20260055532A1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>US12543516B2</t>
+          <t>US20260055532A1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/12543516</t>
+          <t>https://patents.google.com/patent/US20260055532A1/en</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>US18/161,681</t>
+          <t>US18/813,891</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>US20260035835A1</t>
+          <t>WO2026005974A1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>98611688</t>
+          <t>98222733</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>US20260035835A1</t>
+          <t>WO2026005974A1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -19251,39 +20355,39 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260035835</t>
+          <t>https://patents.google.com/patent/WO2026005974A1/en</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>US19/281,879</t>
+          <t>PCT/US2025/032763</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>US20260055532A1</t>
+          <t>WO2026005974A1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US20260055532A1</t>
+          <t>98222733</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>US20260055532A1</t>
+          <t>US20260005044A1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -19293,12 +20397,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260055532A1/en</t>
+          <t>https://patents.google.com/patent/US20260005044A1/en</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>US18/813,891</t>
+          <t>US19/231,136</t>
         </is>
       </c>
     </row>
@@ -19310,22 +20414,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WO2026005974A1</t>
+          <t>US20260009155A1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>98222733</t>
+          <t>98371938</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>WO2026005974A1</t>
+          <t>US20260009155A1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -19335,12 +20439,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026005974A1/en</t>
+          <t>https://patents.google.com/patent/US20260009155A1/en</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>PCT/US2025/032763</t>
+          <t>US18/766,209</t>
         </is>
       </c>
     </row>
@@ -19352,22 +20456,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WO2026005974A1</t>
+          <t>US20260009155A1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>98222733</t>
+          <t>98371938</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>US20260005044A1</t>
+          <t>WO2026015279A1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -19377,12 +20481,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260005044A1/en</t>
+          <t>https://patents.google.com/patent/WO2026015279A1/en</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>US19/231,136</t>
+          <t>PCT/US2025/034927</t>
         </is>
       </c>
     </row>
@@ -19394,37 +20498,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>US20260009155A1</t>
+          <t>US12526971B2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>98371938</t>
+          <t>84891093</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>US20260009155A1</t>
+          <t>US12526971B2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260009155A1/en</t>
+          <t>https://patents.google.com/patent/US12526971B2/en</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>US18/766,209</t>
+          <t>US17/811,323</t>
         </is>
       </c>
     </row>
@@ -19436,17 +20540,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>US20260009155A1</t>
+          <t>US20260015766A1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>98371938</t>
+          <t>98388167</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>WO2026015279A1</t>
+          <t>US20260015766A1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -19461,12 +20565,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026015279A1/en</t>
+          <t>https://patents.google.com/patent/US20260015766A1/en</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>PCT/US2025/034927</t>
+          <t>US19/254,530</t>
         </is>
       </c>
     </row>
@@ -19478,22 +20582,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>US12526971B2</t>
+          <t>KR102915695B1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>84891093</t>
+          <t>69946479</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>US12526971B2</t>
+          <t>KR102915695B1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -19503,12 +20607,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12526971B2/en</t>
+          <t>https://patents.google.com/patent/KR102915695B1/en</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>US17/811,323</t>
+          <t>KR10-2021-7013054</t>
         </is>
       </c>
     </row>
@@ -19520,22 +20624,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>US20260015766A1</t>
+          <t>WO2026016396A1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>98388167</t>
+          <t>93311556</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>US20260015766A1</t>
+          <t>WO2026016396A1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -19545,12 +20649,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260015766A1/en</t>
+          <t>https://patents.google.com/patent/WO2026016396A1/en</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>US19/254,530</t>
+          <t>PCT/CN2024/139537</t>
         </is>
       </c>
     </row>
@@ -19562,37 +20666,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KR102915695B1</t>
+          <t>WO2026024419A1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>69946479</t>
+          <t>98432025</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KR102915695B1</t>
+          <t>WO2026024419A1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR102915695B1/en</t>
+          <t>https://patents.google.com/patent/WO2026024419A1/en</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>KR10-2021-7013054</t>
+          <t>PCT/US2025/035467</t>
         </is>
       </c>
     </row>
@@ -19604,17 +20708,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WO2026016396A1</t>
+          <t>WO2026024419A1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>93311556</t>
+          <t>98432025</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>WO2026016396A1</t>
+          <t>US20260022492A1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -19629,12 +20733,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026016396A1/en</t>
+          <t>https://patents.google.com/patent/US20260022492A1/en</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>PCT/CN2024/139537</t>
+          <t>US18/779,927</t>
         </is>
       </c>
     </row>
@@ -19646,37 +20750,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WO2026024419A1</t>
+          <t>KR102918757B1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>98432025</t>
+          <t>priority-US62-859621</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>WO2026024419A1</t>
+          <t>KR102918757B1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2026024419A1/en</t>
+          <t>https://doi.org/10.8080/1020200063344</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>PCT/US2025/035467</t>
+          <t>KR10-2020-0063344</t>
         </is>
       </c>
     </row>
@@ -19688,17 +20792,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WO2026024419A1</t>
+          <t>US20260026275A1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>98432025</t>
+          <t>98431965</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>US20260022492A1</t>
+          <t>US20260026275A1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -19713,81 +20817,81 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20260022492A1/en</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260026275</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>US18/779,927</t>
+          <t>US18/930,106</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KR102918757B1</t>
+          <t>KR20250168533A</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>priority-US62-859621</t>
+          <t>92898385</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KR102918757B1</t>
+          <t>KR20250168533A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://doi.org/10.8080/1020200063344</t>
+          <t>https://patents.google.com/patent/KR20250168533A/en</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>KR10-2020-0063344</t>
+          <t>KR10-2025-7036006</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>US20260026275A1</t>
+          <t>US20250379096A1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>98431965</t>
+          <t>97917028</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>US20260026275A1</t>
+          <t>US20250379096A1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -19797,12 +20901,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20260026275</t>
+          <t>https://patents.google.com/patent/US20250379096A1/en</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>US18/930,106</t>
+          <t>US18/738,960</t>
         </is>
       </c>
     </row>
@@ -19814,22 +20918,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KR20250168533A</t>
+          <t>US20250379096A1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>92898385</t>
+          <t>97917028</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KR20250168533A</t>
+          <t>WO2025259414A1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -19839,12 +20943,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR20250168533A/en</t>
+          <t>https://patents.google.com/patent/WO2025259414A1/en</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>KR10-2025-7036006</t>
+          <t>PCT/US2025/030002</t>
         </is>
       </c>
     </row>
@@ -19856,22 +20960,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>US20250379096A1</t>
+          <t>US20250385089A1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>97917028</t>
+          <t>96773433</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>US20250379096A1</t>
+          <t>US20250385089A1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -19881,12 +20985,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250379096A1/en</t>
+          <t>https://patents.google.com/patent/US20250385089A1/en</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>US18/738,960</t>
+          <t>US19/034,146</t>
         </is>
       </c>
     </row>
@@ -19898,17 +21002,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>US20250379096A1</t>
+          <t>US20250385122A1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>97917028</t>
+          <t>98012764</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>WO2025259414A1</t>
+          <t>US20250385122A1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -19923,12 +21027,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025259414A1/en</t>
+          <t>https://patents.google.com/patent/US20250385122A1/en</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>PCT/US2025/030002</t>
+          <t>US19/227,313</t>
         </is>
       </c>
     </row>
@@ -19940,17 +21044,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>US20250385089A1</t>
+          <t>US20250385122A1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>96773433</t>
+          <t>98012764</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>US20250385089A1</t>
+          <t>WO2025259500A1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -19965,12 +21069,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250385089A1/en</t>
+          <t>https://patents.google.com/patent/WO2025259500A1/en</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>US19/034,146</t>
+          <t>PCT/US2025/032319</t>
         </is>
       </c>
     </row>
@@ -19982,37 +21086,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>US20250385122A1</t>
+          <t>US12503791B2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>98012764</t>
+          <t>74870666</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>US20250385122A1</t>
+          <t>US12503791B2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250385122A1/en</t>
+          <t>https://patents.google.com/patent/US12503791B2/en</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>US19/227,313</t>
+          <t>US18/548,938</t>
         </is>
       </c>
     </row>
@@ -20024,37 +21128,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>US20250385122A1</t>
+          <t>KR102904356B1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>98012764</t>
+          <t>67768731</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>WO2025259500A1</t>
+          <t>KR102904356B1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025259500A1/en</t>
+          <t>https://patents.google.com/patent/KR102904356B1/en</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>PCT/US2025/032319</t>
+          <t>KR10-2023-7021908</t>
         </is>
       </c>
     </row>
@@ -20066,37 +21170,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>US12503791B2</t>
+          <t>WO2025260942A1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>74870666</t>
+          <t>92856584</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>US12503791B2</t>
+          <t>WO2025260942A1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12503791B2/en</t>
+          <t>https://patents.google.com/patent/WO2025260942A1/en</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>US18/548,938</t>
+          <t>PCT/CN2025/089289</t>
         </is>
       </c>
     </row>
@@ -20108,22 +21212,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KR102904356B1</t>
+          <t>US12512362B2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>67768731</t>
+          <t>92216211</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KR102904356B1</t>
+          <t>US12512362B2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -20133,12 +21237,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR102904356B1/en</t>
+          <t>https://patents.google.com/patent/US12512362B2/en</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>KR10-2023-7021908</t>
+          <t>US18/108,272</t>
         </is>
       </c>
     </row>
@@ -20150,22 +21254,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WO2025260942A1</t>
+          <t>US20250369154A1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>92856584</t>
+          <t>priority-US63-653322</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>WO2025260942A1</t>
+          <t>US20250369154A1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -20175,39 +21279,39 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025260942A1/en</t>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20250369154</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>PCT/CN2025/089289</t>
+          <t>US19/219,468</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>US12512362B2</t>
+          <t>KR102886069B1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>92216211</t>
+          <t>92173251</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>US12512362B2</t>
+          <t>KR102886069B1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -20217,39 +21321,39 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12512362B2/en</t>
+          <t>https://patents.google.com/patent/KR102886069B1/en</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>US18/108,272</t>
+          <t>KR10-2023-0007657</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>US20250369154A1</t>
+          <t>US20250351329A1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>priority-US63-653322</t>
+          <t>97600888</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>US20250369154A1</t>
+          <t>US20250351329A1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -20259,12 +21363,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/20250369154</t>
+          <t>https://patents.google.com/patent/US20250351329A1/en</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>US19/219,468</t>
+          <t>US18/657,458</t>
         </is>
       </c>
     </row>
@@ -20276,17 +21380,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KR102886069B1</t>
+          <t>US20250351329A1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>92173251</t>
+          <t>97600888</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>KR102886069B1</t>
+          <t>WO2025235183A1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -20296,17 +21400,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR102886069B1/en</t>
+          <t>https://patents.google.com/patent/WO2025235183A1/en</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>KR10-2023-0007657</t>
+          <t>PCT/US2025/025467</t>
         </is>
       </c>
     </row>
@@ -20318,37 +21422,37 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>US20250351329A1</t>
+          <t>WO2025232199A1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>97600888</t>
+          <t>91234161</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>US20250351329A1</t>
+          <t>TWI903931B</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250351329A1/en</t>
+          <t>https://patents.google.com/patent/TWI903931B/en</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>US18/657,458</t>
+          <t>TW113149399</t>
         </is>
       </c>
     </row>
@@ -20360,17 +21464,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>US20250351329A1</t>
+          <t>WO2025232199A1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>97600888</t>
+          <t>91234161</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>WO2025235183A1</t>
+          <t>WO2025232199A1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -20385,12 +21489,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025235183A1/en</t>
+          <t>https://patents.google.com/patent/WO2025232199A1/en</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>PCT/US2025/025467</t>
+          <t>PCT/CN2024/139535</t>
         </is>
       </c>
     </row>
@@ -20402,37 +21506,37 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WO2025232199A1</t>
+          <t>TW202544883A</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>91234161</t>
+          <t>96264239</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>TWI903931B</t>
+          <t>TW202544883A</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/TWI903931B/en</t>
+          <t>https://patents.google.com/patent/TW202544883A/en</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>TW113149399</t>
+          <t>TW114100071A</t>
         </is>
       </c>
     </row>
@@ -20444,37 +21548,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WO2025232199A1</t>
+          <t>KR102888301B1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>91234161</t>
+          <t>96708900</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>WO2025232199A1</t>
+          <t>KR102888301B1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025232199A1/en</t>
+          <t>https://patents.google.com/patent/KR102888301B1/en</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>PCT/CN2024/139535</t>
+          <t>KR10-2024-0023762</t>
         </is>
       </c>
     </row>
@@ -20486,22 +21590,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TW202544883A</t>
+          <t>US20250358906A1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>96264239</t>
+          <t>97678423</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>TW202544883A</t>
+          <t>US20250358906A1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -20511,12 +21615,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/TW202544883A/en</t>
+          <t>https://patents.google.com/patent/US20250358906A1/en</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>TW114100071A</t>
+          <t>US18/668,482</t>
         </is>
       </c>
     </row>
@@ -20528,37 +21632,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KR102888301B1</t>
+          <t>US20250358906A1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>96708900</t>
+          <t>97678423</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>KR102888301B1</t>
+          <t>WO2025244852A1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR102888301B1/en</t>
+          <t>https://patents.google.com/patent/WO2025244852A1/en</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>KR10-2024-0023762</t>
+          <t>PCT/US2025/028444</t>
         </is>
       </c>
     </row>
@@ -20570,22 +21674,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>US20250358906A1</t>
+          <t>CN120989593A</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>97678423</t>
+          <t>97692609</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>US20250358906A1</t>
+          <t>CN120989593A</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -20595,12 +21699,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250358906A1/en</t>
+          <t>https://patents.google.com/patent/CN120989593A/en</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>US18/668,482</t>
+          <t>CN202510999081.9</t>
         </is>
       </c>
     </row>
@@ -20612,22 +21716,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>US20250358906A1</t>
+          <t>CN121002222A</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>97678423</t>
+          <t>92898385</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>WO2025244852A1</t>
+          <t>CN121002222A</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -20637,12 +21741,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025244852A1/en</t>
+          <t>https://patents.google.com/patent/CN121002222A/en</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>PCT/US2025/028444</t>
+          <t>CN202480026991.2</t>
         </is>
       </c>
     </row>
@@ -20654,17 +21758,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CN120989593A</t>
+          <t>CN121002231A</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>97692609</t>
+          <t>93216530</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CN120989593A</t>
+          <t>CN121002231A</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -20679,12 +21783,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN120989593A/en</t>
+          <t>https://patents.google.com/patent/CN121002231A/en</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CN202510999081.9</t>
+          <t>CN202480027268.6</t>
         </is>
       </c>
     </row>
@@ -20696,17 +21800,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CN121002222A</t>
+          <t>CN121002616A</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>92898385</t>
+          <t>95483538</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CN121002222A</t>
+          <t>CN121002616A</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -20721,12 +21825,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN121002222A/en</t>
+          <t>https://patents.google.com/patent/CN121002616A/en</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CN202480026991.2</t>
+          <t>CN202480026974.9</t>
         </is>
       </c>
     </row>
@@ -20738,17 +21842,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CN121002231A</t>
+          <t>CN121002621A</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>93216530</t>
+          <t>94372436</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CN121002231A</t>
+          <t>CN121002621A</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -20763,12 +21867,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN121002231A/en</t>
+          <t>https://patents.google.com/patent/CN121002621A/en</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>CN202480027268.6</t>
+          <t>CN202480027271.8</t>
         </is>
       </c>
     </row>
@@ -20780,17 +21884,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CN121002616A</t>
+          <t>KR102889785B1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>95483538</t>
+          <t>75586288</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CN121002616A</t>
+          <t>KR102889785B1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -20800,17 +21904,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN121002616A/en</t>
+          <t>https://patents.google.com/patent/KR102889785B1/en</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CN202480026974.9</t>
+          <t>KR10-2020-0138153</t>
         </is>
       </c>
     </row>
@@ -20822,17 +21926,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CN121002621A</t>
+          <t>TWI905596B</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>94372436</t>
+          <t>69177479</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CN121002621A</t>
+          <t>TWI905596B</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -20842,17 +21946,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN121002621A/en</t>
+          <t>https://patents.google.com/patent/TWI905596B/en</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>CN202480027271.8</t>
+          <t>TW112148712</t>
         </is>
       </c>
     </row>
@@ -20864,22 +21968,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KR102889785B1</t>
+          <t>CN223598701U</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>75586288</t>
+          <t>97736121</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>KR102889785B1</t>
+          <t>CN223598701U</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -20889,12 +21993,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR102889785B1/en</t>
+          <t>https://patents.google.com/patent/CN223598701U/en</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>KR10-2020-0138153</t>
+          <t>CN202422990545.3</t>
         </is>
       </c>
     </row>
@@ -20906,22 +22010,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TWI905596B</t>
+          <t>US12480223B2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>69177479</t>
+          <t>84061018</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>TWI905596B</t>
+          <t>US12480223B2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -20931,12 +22035,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/TWI905596B/en</t>
+          <t>https://patents.google.com/patent/US12480223B2/en</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>TW112148712</t>
+          <t>US17/377,581</t>
         </is>
       </c>
     </row>
@@ -20948,17 +22052,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CN223598701U</t>
+          <t>US12482662B2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>97736121</t>
+          <t>87518802</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CN223598701U</t>
+          <t>US12482662B2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -20973,12 +22077,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/CN223598701U/en</t>
+          <t>https://patents.google.com/patent/US12482662B2/en</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CN202422990545.3</t>
+          <t>US18/168,199</t>
         </is>
       </c>
     </row>
@@ -20990,17 +22094,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>US12480223B2</t>
+          <t>US12484327B2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>84061018</t>
+          <t>88790957</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>US12480223B2</t>
+          <t>US12484327B2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -21015,12 +22119,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12480223B2/en</t>
+          <t>https://patents.google.com/patent/US12484327B2/en</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>US17/377,581</t>
+          <t>US17/663,801</t>
         </is>
       </c>
     </row>
@@ -21032,37 +22136,37 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>US12482662B2</t>
+          <t>US12484327B2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>87518802</t>
+          <t>88790957</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>US12482662B2</t>
+          <t>US20250366243A1</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12482662B2/en</t>
+          <t>https://patents.google.com/patent/US20250366243A1/en</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>US18/168,199</t>
+          <t>US19/290,690</t>
         </is>
       </c>
     </row>
@@ -21074,22 +22178,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>US12484327B2</t>
+          <t>JP7776424B2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>88790957</t>
+          <t>77366308</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>US12484327B2</t>
+          <t>JP7776424B2</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -21099,12 +22203,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12484327B2/en</t>
+          <t>https://patents.google.com/patent/JP7776424B2/en</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>US17/663,801</t>
+          <t>JP2022-543660</t>
         </is>
       </c>
     </row>
@@ -21116,17 +22220,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>US12484327B2</t>
+          <t>DE112021001213B4</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>88790957</t>
+          <t>77391262</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>US20250366243A1</t>
+          <t>DE112021001213B4</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -21136,17 +22240,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250366243A1/en</t>
+          <t>https://patents.google.com/patent/DE112021001213B4/en</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>US19/290,690</t>
+          <t>DE11 2021 001 213.4</t>
         </is>
       </c>
     </row>
@@ -21158,37 +22262,37 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>JP7776424B2</t>
+          <t>WO2025244833A1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>77366308</t>
+          <t>US18/668884</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>JP7776424B2</t>
+          <t>US20250354291A1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP7776424B2/en</t>
+          <t>https://patents.google.com/patent/US20250354291A1/en</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>JP2022-543660</t>
+          <t>US18/668,884</t>
         </is>
       </c>
     </row>
@@ -21200,17 +22304,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DE112021001213B4</t>
+          <t>WO2025244833A1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>77391262</t>
+          <t>US18/668884</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>DE112021001213B4</t>
+          <t>WO2025244833A1</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -21220,44 +22324,44 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/DE112021001213B4/en</t>
+          <t>https://patents.google.com/patent/WO2025244833A1/en</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>DE11 2021 001 213.4</t>
+          <t>PCT/US2025/028039</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>WO2025244833A1</t>
+          <t>US20250324699A1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US18/668884</t>
+          <t>97305113</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>US20250354291A1</t>
+          <t>US20250324699A1</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -21267,39 +22371,39 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250354291A1/en</t>
+          <t>https://patents.google.com/patent/US20250324699A1/en</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>US18/668,884</t>
+          <t>US18/632,863</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>WO2025244833A1</t>
+          <t>US20250324699A1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>US18/668884</t>
+          <t>97305113</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>WO2025244833A1</t>
+          <t>WO2025216831A1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -21309,14 +22413,10 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025244833A1/en</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>PCT/US2025/028039</t>
-        </is>
-      </c>
+          <t>https://patents.google.com/patent/WO2025216831A1/en</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21326,37 +22426,37 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>US20250324699A1</t>
+          <t>US12444605B2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>97305113</t>
+          <t>87068944</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>US20250324699A1</t>
+          <t>US12444605B2</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250324699A1/en</t>
+          <t>https://patents.google.com/patent/US12444605B2/en</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>US18/632,863</t>
+          <t>US17/573,748</t>
         </is>
       </c>
     </row>
@@ -21368,35 +22468,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>US20250324699A1</t>
+          <t>US12454769B2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>97305113</t>
+          <t>69229332</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>WO2025216831A1</t>
+          <t>US12454769B2</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025216831A1/en</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>https://patents.google.com/patent/US12454769B2/en</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>US16/529,066</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -21406,37 +22510,37 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>US12444605B2</t>
+          <t>US20250327211A1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>87068944</t>
+          <t>88730037</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>US12444605B2</t>
+          <t>US20250327211A1</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12444605B2/en</t>
+          <t>https://patents.google.com/patent/US20250327211A1/en</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>US17/573,748</t>
+          <t>US18/861,658</t>
         </is>
       </c>
     </row>
@@ -21448,37 +22552,37 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>US12454769B2</t>
+          <t>WO2025204274A1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>69229332</t>
+          <t>97216439</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>US12454769B2</t>
+          <t>WO2025204274A1</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US12454769B2/en</t>
+          <t>https://patents.google.com/patent/WO2025204274A1/en</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>US16/529,066</t>
+          <t>PCT/JP2025/005254</t>
         </is>
       </c>
     </row>
@@ -21490,22 +22594,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>US20250327211A1</t>
+          <t>WO2025204274A1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>88730037</t>
+          <t>97216439</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>US20250327211A1</t>
+          <t>JP2025153336A</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -21515,14 +22619,10 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250327211A1/en</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>US18/861,658</t>
-        </is>
-      </c>
+          <t>https://patents.google.com/patent/JP2025153336A/en</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21532,22 +22632,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>WO2025204274A1</t>
+          <t>WO2025220436A1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>97216439</t>
+          <t>97403275</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>WO2025204274A1</t>
+          <t>WO2025220436A1</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -21557,12 +22657,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025204274A1/en</t>
+          <t>https://patents.google.com/patent/WO2025220436A1/en</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>PCT/JP2025/005254</t>
+          <t>PCT/JP2025/011481</t>
         </is>
       </c>
     </row>
@@ -21574,22 +22674,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>WO2025204274A1</t>
+          <t>WO2025220436A1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>97216439</t>
+          <t>97403275</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>JP2025153336A</t>
+          <t>JP2025163888A</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -21599,7 +22699,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP2025153336A/en</t>
+          <t>https://patents.google.com/patent/JP2025163888A/en</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -21612,22 +22712,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>WO2025220436A1</t>
+          <t>WO2025225316A1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>97403275</t>
+          <t>97490196</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>WO2025220436A1</t>
+          <t>WO2025225316A1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -21637,12 +22737,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025220436A1/en</t>
+          <t>https://patents.google.com/patent/WO2025225316A1/en</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>PCT/JP2025/011481</t>
+          <t>PCT/JP2025/013571</t>
         </is>
       </c>
     </row>
@@ -21654,17 +22754,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>WO2025220436A1</t>
+          <t>WO2025222891A1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>97403275</t>
+          <t>92004055</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>JP2025163888A</t>
+          <t>WO2025222891A1</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -21679,10 +22779,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP2025163888A/en</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
+          <t>https://patents.google.com/patent/WO2025222891A1/en</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>PCT/CN2024/139550</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21692,22 +22796,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>WO2025225316A1</t>
+          <t>WO2025221932A1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>97490196</t>
+          <t>97404361</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>WO2025225316A1</t>
+          <t>WO2025221932A1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -21717,12 +22821,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025225316A1/en</t>
+          <t>https://patents.google.com/patent/WO2025221932A1/en</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>PCT/JP2025/013571</t>
+          <t>PCT/US2025/025026</t>
         </is>
       </c>
     </row>
@@ -21734,22 +22838,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>WO2025222891A1</t>
+          <t>US20250331222A1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>92004055</t>
+          <t>US14954661-continuations</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>WO2025222891A1</t>
+          <t>US20250331222A1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -21759,12 +22863,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025222891A1/en</t>
+          <t>https://patents.google.com/patent/US20250331222A1/en</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>PCT/CN2024/139550</t>
+          <t>US19/254,559</t>
         </is>
       </c>
     </row>
@@ -21776,22 +22880,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>WO2025221932A1</t>
+          <t>JP2025533523A</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>97404361</t>
+          <t>90455087</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>WO2025221932A1</t>
+          <t>JP2025533523A</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -21801,12 +22905,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025221932A1/en</t>
+          <t>https://patents.google.com/patent/JP2025533523A/en</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>PCT/US2025/025026</t>
+          <t>JP2025517252A</t>
         </is>
       </c>
     </row>
@@ -21818,22 +22922,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>US20250331222A1</t>
+          <t>KR20250150601A</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>US14954661-continuations</t>
+          <t>92905641</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>US20250331222A1</t>
+          <t>KR20250150601A</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -21843,12 +22947,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/US20250331222A1/en</t>
+          <t>https://patents.google.com/patent/KR20250150601A/en</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>US19/254,559</t>
+          <t>KR1020257030522A</t>
         </is>
       </c>
     </row>
@@ -21860,37 +22964,37 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JP2025533523A</t>
+          <t>KR102870814B1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>90455087</t>
+          <t>82495837</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>JP2025533523A</t>
+          <t>KR102870814B1</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>publication</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP2025533523A/en</t>
+          <t>https://patents.google.com/patent/KR102870814B1/en</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>JP2025517252A</t>
+          <t>KR1020237002012A</t>
         </is>
       </c>
     </row>
@@ -21902,22 +23006,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>KR20250150601A</t>
+          <t>KR102870814B1</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>92905641</t>
+          <t>82495837</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>KR20250150601A</t>
+          <t>KR20250151590A</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -21927,12 +23031,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR20250150601A/en</t>
+          <t>https://patents.google.com/patent/TW202244987A/en</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>KR1020257030522A</t>
+          <t>KR1020257033068A</t>
         </is>
       </c>
     </row>
@@ -21944,22 +23048,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>KR102870814B1</t>
+          <t>JP7757917B2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>82495837</t>
+          <t>SUMCO-JP2021180298-carbon-epi</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>KR102870814B1</t>
+          <t>JP7757917B2</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -21969,12 +23073,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/KR102870814B1/en</t>
+          <t>https://patents.google.com/patent/JP7757917B2/en</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>KR1020237002012A</t>
+          <t>JP2022149835A</t>
         </is>
       </c>
     </row>
@@ -21986,22 +23090,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>KR102870814B1</t>
+          <t>JP7757917B2</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>82495837</t>
+          <t>SUMCO-JP2021180298-carbon-epi</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>KR20250151590A</t>
+          <t>JP2025157587A</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -22011,12 +23115,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/TW202244987A/en</t>
+          <t>https://patents.google.com/patent/JP2025157587A/en</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>KR1020257033068A</t>
+          <t>JP2025128738A</t>
         </is>
       </c>
     </row>
@@ -22028,37 +23132,37 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JP7757917B2</t>
+          <t>WO2025211045A1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SUMCO-JP2021180298-carbon-epi</t>
+          <t>97266884</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>JP7757917B2</t>
+          <t>WO2025211045A1</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>grant</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP7757917B2/en</t>
+          <t>https://patents.google.com/patent/WO2025211045A1/en</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>JP2022149835A</t>
+          <t>PCT/JP2025/006194</t>
         </is>
       </c>
     </row>
@@ -22070,17 +23174,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JP7757917B2</t>
+          <t>WO2025211045A1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SUMCO-JP2021180298-carbon-epi</t>
+          <t>97266884</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>JP2025157587A</t>
+          <t>JP2025156774A</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -22095,12 +23199,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP2025157587A/en</t>
+          <t>https://patents.google.com/patent/JP2025156774A/en</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>JP2025128738A</t>
+          <t>JP2024059431A</t>
         </is>
       </c>
     </row>
@@ -22112,22 +23216,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>WO2025211045A1</t>
+          <t>CN120797198A</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>97266884</t>
+          <t>CN202511321399.8</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>WO2025211045A1</t>
+          <t>CN120797198A</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -22137,12 +23241,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/WO2025211045A1/en</t>
+          <t>https://patents.google.com/patent/CN120797198A/en</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>PCT/JP2025/006194</t>
+          <t>CN202511321399.8A</t>
         </is>
       </c>
     </row>
@@ -22154,22 +23258,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>WO2025211045A1</t>
+          <t>US20250327209A1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>97266884</t>
+          <t>US20250327209A1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>JP2025156774A</t>
+          <t>US20250327209A1</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -22179,94 +23283,10 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://patents.google.com/patent/JP2025156774A/en</t>
+          <t>https://patents.google.com/patent/US20250327209A1/en</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
-        <is>
-          <t>JP2024059431A</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>CN120797198A</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>CN202511321399.8</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>CN120797198A</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>publication</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://patents.google.com/patent/CN120797198A/en</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>CN202511321399.8A</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>US20250327209A1</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>US20250327209A1</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>US20250327209A1</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>publication</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://patents.google.com/patent/US20250327209A1/en</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
         <is>
           <t>US19/182,248</t>
         </is>
@@ -22283,7 +23303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22316,6 +23336,14 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="19" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="23" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="48" customWidth="1" min="34" max="34"/>
+    <col width="48" customWidth="1" min="35" max="35"/>
+    <col width="28" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="21" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22467,6 +23495,46 @@
       <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>discovery_source</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>team_independent_read</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>read_disposition</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>read_status</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pending_reason</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>failure_or_pending_reason</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>read_query</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>official_source_url</t>
         </is>
       </c>
     </row>
@@ -22539,6 +23607,26 @@
           <t>independent_search</t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>证据复核 r2：独立检索命中但技术边界（等离子体增强外延 vs 纯 preclean/EPI 主线）与同族引用关系待核；未升格为独立新纳入。基线条目中仅作同族附图引用，不重复升格。</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>证据复核 r2：独立检索命中但技术边界（等离子体增强外延 vs 纯 preclean/EPI 主线）与同族引用关系待核；未升格为独立新纳入。基线条目中仅作同族附图引用，不重复升格。</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>pending_not_promoted</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -22601,6 +23689,26 @@
           <t>independent_search</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>证据复核 r2：独立检索列出，但公开日/全文在复核时未能从官方可访问源稳定取得（Google Patents 404）；保留待核，不入主表。</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>公开号 kind/日期未核实；不得默认 A1 公开。</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>pending_verify_publication</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -22675,6 +23783,26 @@
           <t>reference_report</t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>证据复核 r2：已在基线主表（imported baseline）。独立检索侧列为待核项系同族/自掺杂边界复核，不升级为独立新发现。</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>证据复核 r2：已在基线主表（imported baseline）。独立检索侧列为待核项系同族/自掺杂边界复核，不升级为独立新发现。</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>pending_not_promoted</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -22745,6 +23873,26 @@
           <t>independent_search</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>证据复核 r2：关联外延腔首片工艺，但与核心 EPI/preclean 纳入边界需补读权利要求；暂列待核，不入主表为新发现。</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>证据复核 r2：关联外延腔首片工艺，但与核心 EPI/preclean 纳入边界需补读权利要求；暂列待核，不入主表为新发现。</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>pending_not_promoted</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/patents.xlsx
+++ b/ledger/patents.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -670,10 +670,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>counts.figures_available</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>counts.figures_pending</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Empty months ≠ zero hits. 2025-09 paused. No zero-omission claim.</t>
         </is>
@@ -23645,11 +23665,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>publication</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>

--- a/ledger/patents.xlsx
+++ b/ledger/patents.xlsx
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -23821,7 +23821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23834,9 +23834,9 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
@@ -23852,14 +23852,14 @@
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
     <col width="23" customWidth="1" min="31" max="31"/>
     <col width="18" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="48" customWidth="1" min="34" max="34"/>
     <col width="48" customWidth="1" min="35" max="35"/>
-    <col width="28" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="21" customWidth="1" min="38" max="38"/>
   </cols>
@@ -24184,17 +24184,17 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>US20260066234A1</t>
+          <t>CN122564748A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US20260066234A1</t>
+          <t>CN122564748A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -24213,19 +24213,19 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>等离子体增强外延沉积腔室</t>
+          <t>消除外延腔首片膜厚异常的方法</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>江苏天芯微半导体设备有限公司</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -24254,283 +24254,21 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>已升格 2026-03 主表 core 并计 team_read（r2）；保留队列记录。</t>
+          <t>证据复核 r2：关联外延腔首片工艺，但与核心 EPI/preclean 纳入边界需补读权利要求；暂列待核，不入主表为新发现。</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>证据复核 r2：独立检索命中但技术边界（等离子体增强外延 vs 纯 preclean/EPI 主线）与同族引用关系待核；未升格为独立新纳入。基线条目中仅作同族附图引用，不重复升格。</t>
+          <t>证据复核 r2：关联外延腔首片工艺，但与核心 EPI/preclean 纳入边界需补读权利要求；暂列待核，不入主表为新发现。</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>promoted_core_team_read</t>
+          <t>pending_not_promoted</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>US12757451B2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>US12757451B2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>（公开文献待核实）US12757451B2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>independent_search</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>证据复核 r2：独立检索列出，但公开日/全文在复核时未能从官方可访问源稳定取得（Google Patents 404）；保留待核，不入主表。</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>公开号 kind/日期未核实；不得默认 A1 公开。</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>pending_verify_publication</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>WO2026084898A1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>WO2026084898A1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>WO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>publication</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>控制含硅外延材料中的自掺杂</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Applied Materials, Inc.</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>imported baseline</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>reference_report</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>证据复核 r2：已在基线主表（imported baseline）。独立检索侧列为待核项系同族/自掺杂边界复核，不升级为独立新发现。</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>证据复核 r2：已在基线主表（imported baseline）。独立检索侧列为待核项系同族/自掺杂边界复核，不升级为独立新发现。</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>pending_not_promoted</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CN122564748A</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CN122564748A</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>publication</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>消除外延腔首片膜厚异常的方法</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>江苏天芯微半导体设备有限公司</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>independent_search</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>证据复核 r2：关联外延腔首片工艺，但与核心 EPI/preclean 纳入边界需补读权利要求；暂列待核，不入主表为新发现。</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>证据复核 r2：关联外延腔首片工艺，但与核心 EPI/preclean 纳入边界需补读权利要求；暂列待核，不入主表为新发现。</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>pending_not_promoted</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24591,13 +24329,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
@@ -24721,32 +24459,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>record</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-US12765027B2</t>
-        </is>
-      </c>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T10:40:17Z</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>pending-queue-hygiene</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>prune_pending_or_related</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Removed promoted/excluded from queue: US20260066234A1, US12757451B2, WO2026084898A1</t>
         </is>
       </c>
     </row>
@@ -24758,7 +24492,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-US20260313994A1</t>
+          <t>2026-10-US12765027B2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -24790,7 +24524,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-US12757647B2</t>
+          <t>2026-10-US20260313994A1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -24822,27 +24556,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-US12757648B2</t>
+          <t>2026-10-US12757647B2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-20T10:37:42Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sprint-gap-a</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>content_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -24854,27 +24588,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-US20260304810A1</t>
+          <t>2026-10-US12757648B2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T10:37:42Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>sprint-gap-a</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>content_add</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24620,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-US12727402B2</t>
+          <t>2026-10-US20260304810A1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24918,7 +24652,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-US20260275525A1</t>
+          <t>2026-09-US12727402B2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -24950,7 +24684,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-US20260282506A1</t>
+          <t>2026-09-US20260275525A1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -24982,7 +24716,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-US20260282794A1</t>
+          <t>2026-09-US20260282506A1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -25014,7 +24748,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-US12745604B2</t>
+          <t>2026-09-US20260282794A1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -25046,7 +24780,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-US20260293620A1</t>
+          <t>2026-09-US12745604B2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -25078,7 +24812,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-TWI939895B</t>
+          <t>2026-09-US20260293620A1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -25110,7 +24844,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-US12740346B2</t>
+          <t>2026-09-TWI939895B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -25142,7 +24876,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-US12698570B2</t>
+          <t>2026-09-US12740346B2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -25174,7 +24908,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-US12701762B2</t>
+          <t>2026-08-US12698570B2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -25206,7 +24940,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-US12707938B2</t>
+          <t>2026-08-US12701762B2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -25238,7 +24972,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-US20260250878A1</t>
+          <t>2026-08-US12707938B2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -25270,7 +25004,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-US12701931B2</t>
+          <t>2026-08-US20260250878A1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -25302,7 +25036,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-US20260206272A1</t>
+          <t>2026-08-US12701931B2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -25334,7 +25068,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-US12692621B2</t>
+          <t>2026-07-US20260206272A1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -25366,7 +25100,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-US12696707B2</t>
+          <t>2026-07-US12692621B2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -25398,7 +25132,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-US12680191B2</t>
+          <t>2026-07-US12696707B2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -25430,27 +25164,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-TW202628839A</t>
+          <t>2026-07-US12680191B2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -25462,27 +25196,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-US20260152871A1</t>
+          <t>2026-07-TW202628839A</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25228,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-US12652840B2</t>
+          <t>2026-06-US20260152871A1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -25526,7 +25260,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-US12655537B2</t>
+          <t>2026-06-US12652840B2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -25558,7 +25292,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-US12660266B2</t>
+          <t>2026-06-US12655537B2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -25590,7 +25324,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-JP7882130B2</t>
+          <t>2026-06-US12660266B2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -25622,7 +25356,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-US12672330B2</t>
+          <t>2026-06-JP7882130B2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -25654,7 +25388,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-US20260164725A1</t>
+          <t>2026-06-US12672330B2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25686,27 +25420,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-CN122294515A</t>
+          <t>2026-06-US20260164725A1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -25718,7 +25452,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-US12660522B2</t>
+          <t>2026-06-CN122294515A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -25750,27 +25484,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-US12628600B2</t>
+          <t>2026-06-US12660522B2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -25782,7 +25516,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-US20260136521A1</t>
+          <t>2026-05-US12628600B2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -25819,22 +25553,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>independent_search_confirm</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>独立检索对照命中。保留 reference_report 基线标记，不升级为独立新纳入。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -25846,27 +25580,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-US20260143977A1</t>
+          <t>2026-05-US20260136521A1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_search_confirm</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索对照命中。保留 reference_report 基线标记，不升级为独立新纳入。</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-WO2026101868A1</t>
+          <t>2026-05-US20260143977A1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -25910,7 +25644,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-US20260150594A1</t>
+          <t>2026-05-WO2026101868A1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -25942,27 +25676,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-CN122069948A</t>
+          <t>2026-05-US20260150594A1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -25974,7 +25708,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-WO2026096517A1</t>
+          <t>2026-05-CN122069948A</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -26006,27 +25740,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-US20260092399A1</t>
+          <t>2026-05-WO2026096517A1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -26038,7 +25772,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-JP2026512448A</t>
+          <t>2026-04-US20260092399A1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -26070,7 +25804,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-KR102954223B1</t>
+          <t>2026-04-JP2026512448A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -26102,7 +25836,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-WO2026079031A1</t>
+          <t>2026-04-KR102954223B1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -26134,7 +25868,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-WO2026084898A1</t>
+          <t>2026-04-WO2026079031A1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -26166,7 +25900,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-US20260123349A1</t>
+          <t>2026-04-WO2026084898A1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -26198,7 +25932,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-US12595587B2</t>
+          <t>2026-04-US20260123349A1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -26230,7 +25964,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-US20260068564A1</t>
+          <t>2026-04-US12595587B2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -26262,7 +25996,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-US20260076125A1</t>
+          <t>2026-03-US20260068564A1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -26294,7 +26028,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-WO2026055216A1</t>
+          <t>2026-03-US20260076125A1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -26326,7 +26060,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-KR20260039926A</t>
+          <t>2026-03-WO2026055216A1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -26358,7 +26092,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-03-US20260090293A1</t>
+          <t>2026-03-KR20260039926A</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -26390,7 +26124,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-03-JP2026510085A</t>
+          <t>2026-03-US20260090293A1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -26422,27 +26156,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-03-US20260071979A1</t>
+          <t>2026-03-JP2026510085A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26454,7 +26188,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-CN121693111A</t>
+          <t>2026-03-US20260071979A1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -26486,27 +26220,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-US20260066234A1</t>
+          <t>2026-03-CN121693111A</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-20T12:00:00Z</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>read-ruling-r2</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>promote_core_team_read</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>由 pending 升格 core 月卡；不计为 Gate③ 独立新发现。</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -26518,27 +26252,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-02-US12540400B2</t>
+          <t>2026-03-US20260066234A1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T12:00:00Z</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>read-ruling-r2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>promote_core_team_read</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>由 pending 升格 core 月卡；不计为 Gate③ 独立新发现。</t>
         </is>
       </c>
     </row>
@@ -26550,7 +26284,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-02-US20260043170A1</t>
+          <t>2026-02-US12540400B2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -26582,7 +26316,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-02-US20260047358A1</t>
+          <t>2026-02-US20260043170A1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -26614,7 +26348,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-02-WO2026035639A1</t>
+          <t>2026-02-US20260047358A1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -26646,7 +26380,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-02-CN121519154A</t>
+          <t>2026-02-WO2026035639A1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -26678,7 +26412,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-02-US12557185B2</t>
+          <t>2026-02-CN121519154A</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -26710,7 +26444,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-02-US20260049767A1</t>
+          <t>2026-02-US12557185B2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -26742,7 +26476,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-02-US12564001B2</t>
+          <t>2026-02-US20260049767A1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -26774,7 +26508,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-02-US12543516B2</t>
+          <t>2026-02-US12564001B2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -26811,22 +26545,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>independent_search_confirm</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>独立检索对照命中。保留基线导入属性，仅记录对照复核。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26838,27 +26572,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-02-US20260035835A1</t>
+          <t>2026-02-US12543516B2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_search_confirm</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索对照命中。保留基线导入属性，仅记录对照复核。</t>
         </is>
       </c>
     </row>
@@ -26870,27 +26604,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-02-US20260055532A1</t>
+          <t>2026-02-US20260035835A1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26902,27 +26636,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-01-WO2026005974A1</t>
+          <t>2026-02-US20260055532A1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -26934,7 +26668,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-01-US20260009155A1</t>
+          <t>2026-01-WO2026005974A1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -26966,7 +26700,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-01-US12526971B2</t>
+          <t>2026-01-US20260009155A1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -27003,22 +26737,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>independent_search_confirm</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>独立 EPI 检索再次命中本条（2026-01 授权）。仅作对照确认，仍计为基线导入（imported baseline），不记为本团队新发现。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27030,27 +26764,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-01-US20260015766A1</t>
+          <t>2026-01-US12526971B2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_search_confirm</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立 EPI 检索再次命中本条（2026-01 授权）。仅作对照确认，仍计为基线导入（imported baseline），不记为本团队新发现。</t>
         </is>
       </c>
     </row>
@@ -27062,7 +26796,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-01-KR102915695B1</t>
+          <t>2026-01-US20260015766A1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -27094,7 +26828,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-01-WO2026016396A1</t>
+          <t>2026-01-KR102915695B1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -27126,7 +26860,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-01-WO2026024419A1</t>
+          <t>2026-01-WO2026016396A1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -27158,7 +26892,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-01-KR102918757B1</t>
+          <t>2026-01-WO2026024419A1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -27190,7 +26924,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-01-US20260026275A1</t>
+          <t>2026-01-KR102918757B1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -27222,7 +26956,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2025-12-KR20250168533A</t>
+          <t>2026-01-US20260026275A1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -27254,7 +26988,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2025-12-US20250379096A1</t>
+          <t>2025-12-KR20250168533A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -27286,7 +27020,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2025-12-US20250385089A1</t>
+          <t>2025-12-US20250379096A1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -27318,7 +27052,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2025-12-US20250385122A1</t>
+          <t>2025-12-US20250385089A1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -27350,7 +27084,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2025-12-US12503791B2</t>
+          <t>2025-12-US20250385122A1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -27382,7 +27116,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2025-12-KR102904356B1</t>
+          <t>2025-12-US12503791B2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -27414,7 +27148,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2025-12-WO2025260942A1</t>
+          <t>2025-12-KR102904356B1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -27446,7 +27180,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2025-12-US12512362B2</t>
+          <t>2025-12-WO2025260942A1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -27478,7 +27212,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2025-12-US20250369154A1</t>
+          <t>2025-12-US12512362B2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -27510,7 +27244,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2025-11-KR102886069B1</t>
+          <t>2025-12-US20250369154A1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -27542,7 +27276,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2025-11-US20250351329A1</t>
+          <t>2025-11-KR102886069B1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -27574,7 +27308,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2025-11-WO2025232199A1</t>
+          <t>2025-11-US20250351329A1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -27606,7 +27340,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2025-11-TW202544883A</t>
+          <t>2025-11-WO2025232199A1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -27638,7 +27372,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2025-11-KR102888301B1</t>
+          <t>2025-11-TW202544883A</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -27670,7 +27404,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2025-11-US20250358906A1</t>
+          <t>2025-11-KR102888301B1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -27702,7 +27436,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2025-11-CN120989593A</t>
+          <t>2025-11-US20250358906A1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -27734,7 +27468,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2025-11-CN121002222A</t>
+          <t>2025-11-CN120989593A</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -27766,7 +27500,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2025-11-CN121002231A</t>
+          <t>2025-11-CN121002222A</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -27798,7 +27532,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2025-11-CN121002616A</t>
+          <t>2025-11-CN121002231A</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -27830,7 +27564,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2025-11-CN121002621A</t>
+          <t>2025-11-CN121002616A</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -27862,7 +27596,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2025-11-KR102889785B1</t>
+          <t>2025-11-CN121002621A</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -27894,7 +27628,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2025-11-TWI905596B</t>
+          <t>2025-11-KR102889785B1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -27926,7 +27660,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2025-11-CN223598701U</t>
+          <t>2025-11-TWI905596B</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -27958,7 +27692,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2025-11-US12480223B2</t>
+          <t>2025-11-CN223598701U</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -27990,7 +27724,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2025-11-US12482662B2</t>
+          <t>2025-11-US12480223B2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -28022,7 +27756,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2025-11-US12484327B2</t>
+          <t>2025-11-US12482662B2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -28054,7 +27788,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2025-11-JP7776424B2</t>
+          <t>2025-11-US12484327B2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -28086,7 +27820,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2025-11-DE112021001213B4</t>
+          <t>2025-11-JP7776424B2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -28118,7 +27852,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2025-11-WO2025244833A1</t>
+          <t>2025-11-DE112021001213B4</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -28150,7 +27884,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2025-10-WO2025225316A1</t>
+          <t>2025-11-WO2025244833A1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -28182,7 +27916,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2025-10-WO2025222891A1</t>
+          <t>2025-10-WO2025225316A1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -28214,7 +27948,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2025-10-US12454769B2</t>
+          <t>2025-10-WO2025222891A1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -28246,7 +27980,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2025-10-US20250327211A1</t>
+          <t>2025-10-US12454769B2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -28278,7 +28012,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2025-10-WO2025220436A1</t>
+          <t>2025-10-US20250327211A1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -28310,7 +28044,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2025-10-WO2025221932A1</t>
+          <t>2025-10-WO2025220436A1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -28342,7 +28076,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2025-10-US20250331222A1</t>
+          <t>2025-10-WO2025221932A1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -28374,27 +28108,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2025-10-US20250327209A1</t>
+          <t>2025-10-US20250331222A1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -28406,27 +28140,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2025-10-JP7757917B2</t>
+          <t>2025-10-US20250327209A1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -28438,7 +28172,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2025-10-KR20250150601A</t>
+          <t>2025-10-JP7757917B2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -28470,7 +28204,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2025-10-CN120797198A</t>
+          <t>2025-10-KR20250150601A</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -28502,7 +28236,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2025-10-US20250324699A1</t>
+          <t>2025-10-CN120797198A</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -28534,7 +28268,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2025-10-US12444605B2</t>
+          <t>2025-10-US20250324699A1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -28566,7 +28300,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2025-10-KR102870814B1</t>
+          <t>2025-10-US12444605B2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -28598,7 +28332,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2025-10-WO2025211045A1</t>
+          <t>2025-10-KR102870814B1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -28630,7 +28364,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2025-10-JP2025533523A</t>
+          <t>2025-10-WO2025211045A1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -28662,7 +28396,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2025-10-WO2025204274A1</t>
+          <t>2025-10-JP2025533523A</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -28694,25 +28428,57 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
+          <t>2025-10-WO2025204274A1</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-10-20T17:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>baseline-import</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>2025-10-US20250311241A1</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>2026-10-20T10:37:42Z</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>sprint-gap-a</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>content_add</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
         </is>

--- a/ledger/patents.xlsx
+++ b/ledger/patents.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18">
@@ -3975,7 +3975,7 @@
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
@@ -6142,7 +6142,7 @@
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr">
@@ -23821,7 +23821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23853,13 +23853,13 @@
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
     <col width="23" customWidth="1" min="31" max="31"/>
     <col width="18" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="48" customWidth="1" min="34" max="34"/>
-    <col width="48" customWidth="1" min="35" max="35"/>
-    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="27" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="21" customWidth="1" min="38" max="38"/>
   </cols>
@@ -24179,96 +24179,6 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CN122564748A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CN122564748A</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>publication</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>消除外延腔首片膜厚异常的方法</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>江苏天芯微半导体设备有限公司</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>independent_search</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>证据复核 r2：关联外延腔首片工艺，但与核心 EPI/preclean 纳入边界需补读权利要求；暂列待核，不入主表为新发现。</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>证据复核 r2：关联外延腔首片工艺，但与核心 EPI/preclean 纳入边界需补读权利要求；暂列待核，不入主表为新发现。</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>pending_not_promoted</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24329,14 +24239,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -24487,96 +24397,84 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>record</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-US12765027B2</t>
-        </is>
-      </c>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T10:37:57Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>epi-4-maintenance</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>empty_incremental_research_through_bump</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>epi-4 实际定时触发 empty incremental (dual-track 0/0/0); research_through 2026-10-19→2026-10-20; team_read unchanged 6; log docs/runs/2026-10-20-epi-4-full-maintenance.md; evidence docs/EVIDENCE-DIFF-2026-10-20-epi-4.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>record</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-US20260313994A1</t>
-        </is>
-      </c>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T10:50:56Z</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>preclean-figure-backfill</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>apply_preclean_report_figures</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>WO/TW hybrid-preclean Gate③ figure paths from Preclean backfill manifest.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>record</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-US12757647B2</t>
-        </is>
-      </c>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T10:50:56Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>cn-pending-exclude</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>clear_pending_or_related</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Removed from queue (exclude): CN122564748A</t>
         </is>
       </c>
     </row>
@@ -24588,27 +24486,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-US12757648B2</t>
+          <t>2026-10-US12765027B2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-20T10:37:42Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sprint-gap-a</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>content_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -24620,7 +24518,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-US20260304810A1</t>
+          <t>2026-10-US20260313994A1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24652,7 +24550,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-US12727402B2</t>
+          <t>2026-10-US12757647B2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -24684,27 +24582,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-US20260275525A1</t>
+          <t>2026-10-US12757648B2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T10:37:42Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>sprint-gap-a</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>content_add</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24614,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-US20260282506A1</t>
+          <t>2026-10-US20260304810A1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -24748,7 +24646,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-US20260282794A1</t>
+          <t>2026-09-US12727402B2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -24780,7 +24678,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-US12745604B2</t>
+          <t>2026-09-US20260275525A1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24812,7 +24710,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-US20260293620A1</t>
+          <t>2026-09-US20260282506A1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -24844,7 +24742,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-TWI939895B</t>
+          <t>2026-09-US20260282794A1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -24876,7 +24774,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-US12740346B2</t>
+          <t>2026-09-US12745604B2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24908,7 +24806,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-US12698570B2</t>
+          <t>2026-09-US20260293620A1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24940,7 +24838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-US12701762B2</t>
+          <t>2026-09-TWI939895B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -24972,7 +24870,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-US12707938B2</t>
+          <t>2026-09-US12740346B2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -25004,7 +24902,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-US20260250878A1</t>
+          <t>2026-08-US12698570B2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -25036,7 +24934,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-US12701931B2</t>
+          <t>2026-08-US12701762B2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -25068,7 +24966,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-US20260206272A1</t>
+          <t>2026-08-US12707938B2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -25100,7 +24998,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-US12692621B2</t>
+          <t>2026-08-US20260250878A1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -25132,7 +25030,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-US12696707B2</t>
+          <t>2026-08-US12701931B2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -25164,7 +25062,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-US12680191B2</t>
+          <t>2026-07-US20260206272A1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -25196,27 +25094,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-TW202628839A</t>
+          <t>2026-07-US12692621B2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -25228,7 +25126,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-US20260152871A1</t>
+          <t>2026-07-US12696707B2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -25260,7 +25158,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-US12652840B2</t>
+          <t>2026-07-US12680191B2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -25292,27 +25190,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-US12655537B2</t>
+          <t>2026-07-TW202628839A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -25324,27 +25222,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-US12660266B2</t>
+          <t>2026-07-TW202628839A</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T10:50:56Z</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>preclean-figure-backfill</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Applied 3 figures from PRECLEAN-REPORT-FIGURES-BACKFILL-2026-10-20.json</t>
         </is>
       </c>
     </row>
@@ -25356,7 +25254,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-JP7882130B2</t>
+          <t>2026-06-US20260152871A1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -25388,7 +25286,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-US12672330B2</t>
+          <t>2026-06-US12652840B2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25420,7 +25318,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-US20260164725A1</t>
+          <t>2026-06-US12655537B2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -25452,27 +25350,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-CN122294515A</t>
+          <t>2026-06-US12660266B2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -25484,27 +25382,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-US12660522B2</t>
+          <t>2026-06-JP7882130B2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -25516,7 +25414,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-US12628600B2</t>
+          <t>2026-06-US12672330B2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -25548,7 +25446,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-US20260136521A1</t>
+          <t>2026-06-US20260164725A1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -25580,7 +25478,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-US20260136521A1</t>
+          <t>2026-06-CN122294515A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -25595,12 +25493,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>independent_search_confirm</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>独立检索对照命中。保留 reference_report 基线标记，不升级为独立新纳入。</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -25612,27 +25510,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-US20260143977A1</t>
+          <t>2026-06-US12660522B2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -25644,7 +25542,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-WO2026101868A1</t>
+          <t>2026-05-US12628600B2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -25676,7 +25574,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-US20260150594A1</t>
+          <t>2026-05-US20260136521A1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -25708,7 +25606,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-CN122069948A</t>
+          <t>2026-05-US20260136521A1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -25723,12 +25621,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>independent_search_confirm</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>独立检索对照命中。保留 reference_report 基线标记，不升级为独立新纳入。</t>
         </is>
       </c>
     </row>
@@ -25740,27 +25638,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-WO2026096517A1</t>
+          <t>2026-05-US20260143977A1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -25772,7 +25670,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-US20260092399A1</t>
+          <t>2026-05-WO2026101868A1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -25804,7 +25702,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-JP2026512448A</t>
+          <t>2026-05-US20260150594A1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -25836,27 +25734,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-KR102954223B1</t>
+          <t>2026-05-CN122069948A</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -25868,27 +25766,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-WO2026079031A1</t>
+          <t>2026-05-WO2026096517A1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -25900,27 +25798,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-WO2026084898A1</t>
+          <t>2026-05-WO2026096517A1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T10:50:56Z</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>preclean-figure-backfill</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Applied 3 figures from PRECLEAN-REPORT-FIGURES-BACKFILL-2026-10-20.json</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25830,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-US20260123349A1</t>
+          <t>2026-04-US20260092399A1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -25964,7 +25862,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-04-US12595587B2</t>
+          <t>2026-04-JP2026512448A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -25996,7 +25894,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-US20260068564A1</t>
+          <t>2026-04-KR102954223B1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -26028,7 +25926,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-US20260076125A1</t>
+          <t>2026-04-WO2026079031A1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -26060,7 +25958,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-WO2026055216A1</t>
+          <t>2026-04-WO2026084898A1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -26092,7 +25990,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-03-KR20260039926A</t>
+          <t>2026-04-US20260123349A1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -26124,7 +26022,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-03-US20260090293A1</t>
+          <t>2026-04-US12595587B2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -26156,7 +26054,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-03-JP2026510085A</t>
+          <t>2026-03-US20260068564A1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -26188,27 +26086,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-US20260071979A1</t>
+          <t>2026-03-US20260076125A1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26220,27 +26118,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-CN121693111A</t>
+          <t>2026-03-WO2026055216A1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26252,27 +26150,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-US20260066234A1</t>
+          <t>2026-03-KR20260039926A</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-20T12:00:00Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>read-ruling-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>promote_core_team_read</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>由 pending 升格 core 月卡；不计为 Gate③ 独立新发现。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26284,7 +26182,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-02-US12540400B2</t>
+          <t>2026-03-US20260090293A1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -26316,7 +26214,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-02-US20260043170A1</t>
+          <t>2026-03-JP2026510085A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -26348,27 +26246,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-02-US20260047358A1</t>
+          <t>2026-03-US20260071979A1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -26380,27 +26278,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-02-WO2026035639A1</t>
+          <t>2026-03-CN121693111A</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -26412,27 +26310,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-02-CN121519154A</t>
+          <t>2026-03-US20260066234A1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T12:00:00Z</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>read-ruling-r2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>promote_core_team_read</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>由 pending 升格 core 月卡；不计为 Gate③ 独立新发现。</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26342,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-02-US12557185B2</t>
+          <t>2026-02-US12540400B2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -26476,7 +26374,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-02-US20260049767A1</t>
+          <t>2026-02-US20260043170A1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -26508,7 +26406,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-02-US12564001B2</t>
+          <t>2026-02-US20260047358A1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -26540,7 +26438,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-02-US12543516B2</t>
+          <t>2026-02-WO2026035639A1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -26572,27 +26470,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-02-US12543516B2</t>
+          <t>2026-02-CN121519154A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>independent_search_confirm</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>独立检索对照命中。保留基线导入属性，仅记录对照复核。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26604,7 +26502,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-02-US20260035835A1</t>
+          <t>2026-02-US12557185B2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -26636,27 +26534,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-02-US20260055532A1</t>
+          <t>2026-02-US20260049767A1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26668,7 +26566,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-01-WO2026005974A1</t>
+          <t>2026-02-US12564001B2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -26700,7 +26598,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-01-US20260009155A1</t>
+          <t>2026-02-US12543516B2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -26732,27 +26630,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-01-US12526971B2</t>
+          <t>2026-02-US12543516B2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_search_confirm</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索对照命中。保留基线导入属性，仅记录对照复核。</t>
         </is>
       </c>
     </row>
@@ -26764,27 +26662,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-01-US12526971B2</t>
+          <t>2026-02-US20260035835A1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>independent_search_confirm</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>独立 EPI 检索再次命中本条（2026-01 授权）。仅作对照确认，仍计为基线导入（imported baseline），不记为本团队新发现。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26796,27 +26694,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-01-US20260015766A1</t>
+          <t>2026-02-US20260055532A1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -26828,7 +26726,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-01-KR102915695B1</t>
+          <t>2026-01-WO2026005974A1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -26860,7 +26758,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-01-WO2026016396A1</t>
+          <t>2026-01-US20260009155A1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -26892,7 +26790,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-01-WO2026024419A1</t>
+          <t>2026-01-US12526971B2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -26924,27 +26822,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-01-KR102918757B1</t>
+          <t>2026-01-US12526971B2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_search_confirm</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立 EPI 检索再次命中本条（2026-01 授权）。仅作对照确认，仍计为基线导入（imported baseline），不记为本团队新发现。</t>
         </is>
       </c>
     </row>
@@ -26956,7 +26854,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-01-US20260026275A1</t>
+          <t>2026-01-US20260015766A1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -26988,7 +26886,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2025-12-KR20250168533A</t>
+          <t>2026-01-KR102915695B1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -27020,7 +26918,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2025-12-US20250379096A1</t>
+          <t>2026-01-WO2026016396A1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -27052,7 +26950,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2025-12-US20250385089A1</t>
+          <t>2026-01-WO2026024419A1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -27084,7 +26982,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2025-12-US20250385122A1</t>
+          <t>2026-01-KR102918757B1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -27116,7 +27014,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2025-12-US12503791B2</t>
+          <t>2026-01-US20260026275A1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -27148,7 +27046,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2025-12-KR102904356B1</t>
+          <t>2025-12-KR20250168533A</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -27180,7 +27078,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2025-12-WO2025260942A1</t>
+          <t>2025-12-US20250379096A1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -27212,7 +27110,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2025-12-US12512362B2</t>
+          <t>2025-12-US20250385089A1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -27244,7 +27142,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2025-12-US20250369154A1</t>
+          <t>2025-12-US20250385122A1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -27276,7 +27174,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2025-11-KR102886069B1</t>
+          <t>2025-12-US12503791B2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -27308,7 +27206,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2025-11-US20250351329A1</t>
+          <t>2025-12-KR102904356B1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -27340,7 +27238,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2025-11-WO2025232199A1</t>
+          <t>2025-12-WO2025260942A1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -27372,7 +27270,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2025-11-TW202544883A</t>
+          <t>2025-12-US12512362B2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -27404,7 +27302,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2025-11-KR102888301B1</t>
+          <t>2025-12-US20250369154A1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -27436,7 +27334,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2025-11-US20250358906A1</t>
+          <t>2025-11-KR102886069B1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -27468,7 +27366,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2025-11-CN120989593A</t>
+          <t>2025-11-US20250351329A1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -27500,7 +27398,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2025-11-CN121002222A</t>
+          <t>2025-11-WO2025232199A1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -27532,7 +27430,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2025-11-CN121002231A</t>
+          <t>2025-11-TW202544883A</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -27564,7 +27462,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2025-11-CN121002616A</t>
+          <t>2025-11-KR102888301B1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -27596,7 +27494,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2025-11-CN121002621A</t>
+          <t>2025-11-US20250358906A1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -27628,7 +27526,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2025-11-KR102889785B1</t>
+          <t>2025-11-CN120989593A</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -27660,7 +27558,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2025-11-TWI905596B</t>
+          <t>2025-11-CN121002222A</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -27692,7 +27590,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2025-11-CN223598701U</t>
+          <t>2025-11-CN121002231A</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -27724,7 +27622,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2025-11-US12480223B2</t>
+          <t>2025-11-CN121002616A</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -27756,7 +27654,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2025-11-US12482662B2</t>
+          <t>2025-11-CN121002621A</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -27788,7 +27686,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2025-11-US12484327B2</t>
+          <t>2025-11-KR102889785B1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -27820,7 +27718,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2025-11-JP7776424B2</t>
+          <t>2025-11-TWI905596B</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -27852,7 +27750,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2025-11-DE112021001213B4</t>
+          <t>2025-11-CN223598701U</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -27884,7 +27782,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2025-11-WO2025244833A1</t>
+          <t>2025-11-US12480223B2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -27916,7 +27814,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2025-10-WO2025225316A1</t>
+          <t>2025-11-US12482662B2</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -27948,7 +27846,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2025-10-WO2025222891A1</t>
+          <t>2025-11-US12484327B2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -27980,7 +27878,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2025-10-US12454769B2</t>
+          <t>2025-11-JP7776424B2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -28012,7 +27910,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2025-10-US20250327211A1</t>
+          <t>2025-11-DE112021001213B4</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -28044,7 +27942,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2025-10-WO2025220436A1</t>
+          <t>2025-11-WO2025244833A1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -28076,7 +27974,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2025-10-WO2025221932A1</t>
+          <t>2025-10-WO2025225316A1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -28108,7 +28006,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2025-10-US20250331222A1</t>
+          <t>2025-10-WO2025222891A1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -28140,27 +28038,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2025-10-US20250327209A1</t>
+          <t>2025-10-US12454769B2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -28172,7 +28070,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2025-10-JP7757917B2</t>
+          <t>2025-10-US20250327211A1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -28204,7 +28102,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2025-10-KR20250150601A</t>
+          <t>2025-10-WO2025220436A1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -28236,7 +28134,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2025-10-CN120797198A</t>
+          <t>2025-10-WO2025221932A1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -28268,7 +28166,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2025-10-US20250324699A1</t>
+          <t>2025-10-US20250331222A1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -28300,27 +28198,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2025-10-US12444605B2</t>
+          <t>2025-10-US20250327209A1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -28332,7 +28230,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2025-10-KR102870814B1</t>
+          <t>2025-10-JP7757917B2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -28364,7 +28262,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2025-10-WO2025211045A1</t>
+          <t>2025-10-KR20250150601A</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -28396,7 +28294,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2025-10-JP2025533523A</t>
+          <t>2025-10-CN120797198A</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -28428,7 +28326,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2025-10-WO2025204274A1</t>
+          <t>2025-10-US20250324699A1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -28460,25 +28358,185 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
+          <t>2025-10-US12444605B2</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-10-20T17:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>baseline-import</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2025-10-KR102870814B1</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-10-20T17:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>baseline-import</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2025-10-WO2025211045A1</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-10-20T17:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>baseline-import</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2025-10-JP2025533523A</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-10-20T17:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>baseline-import</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025-10-WO2025204274A1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-10-20T17:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>baseline-import</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>2025-10-US20250311241A1</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>2026-10-20T10:37:42Z</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>sprint-gap-a</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>content_add</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
         </is>

--- a/ledger/patents.xlsx
+++ b/ledger/patents.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>170</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18">
@@ -1054,7 +1054,7 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
@@ -25651,7 +25651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F167"/>
+  <dimension ref="A1:F170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26201,32 +26201,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>record</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-10-US12770834B2</t>
-        </is>
-      </c>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-22T01:54:01Z</t>
+          <t>2026-10-22T12:51:05Z</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>morning-epi-overlap-backfill</t>
+          <t>evening-r4-figure-extract</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>include_core_overlap_backfill</t>
+          <t>apply_evening_r4e_uspto_figures</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EPI-INCREMENTAL-SPRINT-morning-2026-10-22-frozen.json; EVIDENCE-MORNING-DIFF-2026-10-22 PASS_INCREMENTAL</t>
+          <t>US12770834B2+US12768074B2 drawing sheets; pubs=2; actually_read/research_through/team_read untouched by design</t>
         </is>
       </c>
     </row>
@@ -26238,7 +26234,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-US12768074B2</t>
+          <t>2026-10-US12770834B2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -26270,27 +26266,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-US12765027B2</t>
+          <t>2026-10-US12770834B2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-22T12:51:05Z</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evening-r4-figure-extract</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_uspto_drawing_sheet_figures</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Track A evening R4: 8 real USPTO drawing-sheet PNGs; team_read lock unchanged</t>
         </is>
       </c>
     </row>
@@ -26302,27 +26298,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-US20260313994A1</t>
+          <t>2026-10-US12768074B2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-22T01:54:01Z</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>morning-epi-overlap-backfill</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>include_core_overlap_backfill</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>EPI-INCREMENTAL-SPRINT-morning-2026-10-22-frozen.json; EVIDENCE-MORNING-DIFF-2026-10-22 PASS_INCREMENTAL</t>
         </is>
       </c>
     </row>
@@ -26334,27 +26330,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-US12757647B2</t>
+          <t>2026-10-US12768074B2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-22T12:51:05Z</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evening-r4-figure-extract</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_uspto_drawing_sheet_figures</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Track A evening R4: 13 real USPTO drawing-sheet PNGs; team_read lock unchanged</t>
         </is>
       </c>
     </row>
@@ -26366,27 +26362,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-US12757648B2</t>
+          <t>2026-10-US12765027B2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-20T10:37:42Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sprint-gap-a</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>content_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26398,27 +26394,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-US12757648B2</t>
+          <t>2026-10-US20260313994A1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-21T02:07:37Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>morning-gate3-figures</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gate③ backfill 1 figures</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26430,27 +26426,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-US12757665B2</t>
+          <t>2026-10-US12757647B2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-20T13:00:00Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>evening-incremental-sprint</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>include_core_preclean_family</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PRECLEAN-INCREMENTAL-SPRINT-evening-2026-10-20-frozen.json</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -26462,27 +26458,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-US12757665B2</t>
+          <t>2026-10-US12757648B2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-21T02:07:37Z</t>
+          <t>2026-10-20T10:37:42Z</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>morning-gate3-figures</t>
+          <t>sprint-gap-a</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>content_add</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gate③ backfill 6 figures</t>
+          <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
         </is>
       </c>
     </row>
@@ -26494,27 +26490,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-US20260304810A1</t>
+          <t>2026-10-US12757648B2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>morning-gate3-figures</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Gate③ backfill 1 figures</t>
         </is>
       </c>
     </row>
@@ -26526,27 +26522,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-US12727402B2</t>
+          <t>2026-10-US12757665B2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T13:00:00Z</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evening-incremental-sprint</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>include_core_preclean_family</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>PRECLEAN-INCREMENTAL-SPRINT-evening-2026-10-20-frozen.json</t>
         </is>
       </c>
     </row>
@@ -26558,27 +26554,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-US20260275525A1</t>
+          <t>2026-10-US12757665B2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>morning-gate3-figures</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Gate③ backfill 6 figures</t>
         </is>
       </c>
     </row>
@@ -26590,7 +26586,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-US20260282506A1</t>
+          <t>2026-10-US20260304810A1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -26622,7 +26618,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-US20260282794A1</t>
+          <t>2026-09-US12727402B2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -26654,7 +26650,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-US12745604B2</t>
+          <t>2026-09-US20260275525A1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -26686,7 +26682,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-US20260293620A1</t>
+          <t>2026-09-US20260282506A1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -26718,7 +26714,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-TWI939895B</t>
+          <t>2026-09-US20260282794A1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -26750,7 +26746,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-US12740346B2</t>
+          <t>2026-09-US12745604B2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -26782,7 +26778,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-US12698570B2</t>
+          <t>2026-09-US20260293620A1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -26814,7 +26810,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-US12701762B2</t>
+          <t>2026-09-TWI939895B</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -26846,7 +26842,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-US12707938B2</t>
+          <t>2026-09-US12740346B2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -26878,7 +26874,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-US20260250878A1</t>
+          <t>2026-08-US12698570B2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -26910,7 +26906,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-US12701931B2</t>
+          <t>2026-08-US12701762B2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -26942,7 +26938,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-07-US20260206272A1</t>
+          <t>2026-08-US12707938B2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -26974,7 +26970,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-US12692621B2</t>
+          <t>2026-08-US20260250878A1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -27006,7 +27002,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-07-US12696707B2</t>
+          <t>2026-08-US12701931B2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -27038,7 +27034,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-US12680191B2</t>
+          <t>2026-07-US20260206272A1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -27070,27 +27066,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-TW202628839A</t>
+          <t>2026-07-US12692621B2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27102,27 +27098,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-07-TW202628839A</t>
+          <t>2026-07-US12696707B2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-20T10:50:56Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>preclean-figure-backfill</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Applied 3 figures from PRECLEAN-REPORT-FIGURES-BACKFILL-2026-10-20.json</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27134,7 +27130,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-JP7882130B2</t>
+          <t>2026-07-US12680191B2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -27166,27 +27162,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-US12672330B2</t>
+          <t>2026-07-TW202628839A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -27198,27 +27194,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-CN122294515A</t>
+          <t>2026-07-TW202628839A</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T10:50:56Z</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>preclean-figure-backfill</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Applied 3 figures from PRECLEAN-REPORT-FIGURES-BACKFILL-2026-10-20.json</t>
         </is>
       </c>
     </row>
@@ -27230,27 +27226,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-CN122294515A</t>
+          <t>2026-06-JP7882130B2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-20T13:05:00Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>preclean-cn-figure-stamp</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>attach_depats_figures</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gate③ Preclean CN DEPATISnet 附图 1–3（spotcheck PASS）</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27262,7 +27258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-US12655537B2</t>
+          <t>2026-06-US12672330B2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -27294,27 +27290,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-US12660266B2</t>
+          <t>2026-06-CN122294515A</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -27326,27 +27322,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-US12660522B2</t>
+          <t>2026-06-CN122294515A</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T13:05:00Z</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>preclean-cn-figure-stamp</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>attach_depats_figures</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Gate③ Preclean CN DEPATISnet 附图 1–3（spotcheck PASS）</t>
         </is>
       </c>
     </row>
@@ -27358,27 +27354,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-US12660522B2</t>
+          <t>2026-06-US12655537B2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-21T02:07:37Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>morning-gate3-figures</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gate③ backfill 1 figures</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27390,27 +27386,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-US12660544B2</t>
+          <t>2026-06-US12660266B2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-20T13:00:00Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>evening-incremental-sprint</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>include_core_preclean_family</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PRECLEAN-INCREMENTAL-SPRINT-evening-2026-10-20-frozen.json</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27422,27 +27418,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-US12660544B2</t>
+          <t>2026-06-US12660522B2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-21T02:07:37Z</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>morning-gate3-figures</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gate③ backfill 6 figures</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -27454,27 +27450,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-US20260164725A1</t>
+          <t>2026-06-US12660522B2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>morning-gate3-figures</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Gate③ backfill 1 figures</t>
         </is>
       </c>
     </row>
@@ -27486,27 +27482,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-US12652840B2</t>
+          <t>2026-06-US12660544B2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T13:00:00Z</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evening-incremental-sprint</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>include_core_preclean_family</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>PRECLEAN-INCREMENTAL-SPRINT-evening-2026-10-20-frozen.json</t>
         </is>
       </c>
     </row>
@@ -27518,27 +27514,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-06-US20260152871A1</t>
+          <t>2026-06-US12660544B2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>morning-gate3-figures</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Gate③ backfill 6 figures</t>
         </is>
       </c>
     </row>
@@ -27550,7 +27546,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-05-US12628600B2</t>
+          <t>2026-06-US20260164725A1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -27582,7 +27578,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-05-US20260136521A1</t>
+          <t>2026-06-US12652840B2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -27614,27 +27610,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-US20260136521A1</t>
+          <t>2026-06-US20260152871A1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>independent_search_confirm</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>独立检索对照命中。保留 reference_report 基线标记，不升级为独立新纳入。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27646,7 +27642,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-US20260143977A1</t>
+          <t>2026-05-US12628600B2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -27678,7 +27674,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-05-WO2026101868A1</t>
+          <t>2026-05-US20260136521A1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -27710,27 +27706,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-05-US20260150594A1</t>
+          <t>2026-05-US20260136521A1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_search_confirm</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索对照命中。保留 reference_report 基线标记，不升级为独立新纳入。</t>
         </is>
       </c>
     </row>
@@ -27742,27 +27738,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-CN122069948A</t>
+          <t>2026-05-US20260143977A1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27774,27 +27770,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-CN122069948A</t>
+          <t>2026-05-WO2026101868A1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-20T13:05:00Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>preclean-cn-figure-stamp</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>attach_depats_figures</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gate③ Preclean CN DEPATISnet 附图 1–3（spotcheck PASS）</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27806,27 +27802,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-05-WO2026096517A1</t>
+          <t>2026-05-US20260150594A1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -27838,27 +27834,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-WO2026096517A1</t>
+          <t>2026-05-CN122069948A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-20T10:50:56Z</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>preclean-figure-backfill</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Applied 3 figures from PRECLEAN-REPORT-FIGURES-BACKFILL-2026-10-20.json</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -27870,27 +27866,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-04-US20260092399A1</t>
+          <t>2026-05-CN122069948A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T13:05:00Z</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>preclean-cn-figure-stamp</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_depats_figures</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Gate③ Preclean CN DEPATISnet 附图 1–3（spotcheck PASS）</t>
         </is>
       </c>
     </row>
@@ -27902,27 +27898,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-04-JP2026512448A</t>
+          <t>2026-05-WO2026096517A1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -27934,27 +27930,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-04-KR102954223B1</t>
+          <t>2026-05-WO2026096517A1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T10:50:56Z</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>preclean-figure-backfill</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Applied 3 figures from PRECLEAN-REPORT-FIGURES-BACKFILL-2026-10-20.json</t>
         </is>
       </c>
     </row>
@@ -27966,7 +27962,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-04-WO2026079031A1</t>
+          <t>2026-04-US20260092399A1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -27998,7 +27994,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-04-WO2026084898A1</t>
+          <t>2026-04-JP2026512448A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -28030,7 +28026,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-04-US20260123349A1</t>
+          <t>2026-04-KR102954223B1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -28062,7 +28058,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-04-US12595587B2</t>
+          <t>2026-04-WO2026079031A1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -28094,7 +28090,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-03-JP2026510085A</t>
+          <t>2026-04-WO2026084898A1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -28126,7 +28122,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-03-US20260090293A1</t>
+          <t>2026-04-US20260123349A1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -28158,27 +28154,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-03-US20260090293A1</t>
+          <t>2026-04-US12595587B2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-20T13:00:00Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>evening-incremental-sprint</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>label_baseline_preclean_tag</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>US20260090293A1 已 live baseline；补 Preclean 技术标签（claim12），不计晚间新发现。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -28190,7 +28186,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-KR20260039926A</t>
+          <t>2026-03-JP2026510085A</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -28222,27 +28218,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-03-CN121693111A</t>
+          <t>2026-03-US20260090293A1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -28254,27 +28250,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-03-CN121693111A</t>
+          <t>2026-03-US20260090293A1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-20T12:50:00Z</t>
+          <t>2026-10-20T13:00:00Z</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>epi-gate3-cn-figure-backfill</t>
+          <t>evening-incremental-sprint</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>attach_fig1_depats</t>
+          <t>label_baseline_preclean_tag</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Official drawing page 1/3 → assets/figures/CN121693111A_fig1.png (08612a81…).</t>
+          <t>US20260090293A1 已 live baseline；补 Preclean 技术标签（claim12），不计晚间新发现。</t>
         </is>
       </c>
     </row>
@@ -28286,7 +28282,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-03-US20260076125A1</t>
+          <t>2026-03-KR20260039926A</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -28318,27 +28314,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-WO2026055216A1</t>
+          <t>2026-03-CN121693111A</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -28350,27 +28346,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-US20260071979A1</t>
+          <t>2026-03-CN121693111A</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T12:50:00Z</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>epi-gate3-cn-figure-backfill</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>attach_fig1_depats</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Official drawing page 1/3 → assets/figures/CN121693111A_fig1.png (08612a81…).</t>
         </is>
       </c>
     </row>
@@ -28382,27 +28378,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-US20260071979A1</t>
+          <t>2026-03-US20260076125A1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-21T02:07:37Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>morning-gate3-figures</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gate③ backfill 1 figures</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -28414,7 +28410,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-US20260068564A1</t>
+          <t>2026-03-WO2026055216A1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -28446,27 +28442,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-US20260066234A1</t>
+          <t>2026-03-US20260071979A1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-20T12:00:00Z</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>read-ruling-r2</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>promote_core_team_read</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>由 pending 升格 core 月卡；不计为 Gate③ 独立新发现。</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -28478,7 +28474,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-US20260066234A1</t>
+          <t>2026-03-US20260071979A1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -28510,27 +28506,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-US20260062803A1</t>
+          <t>2026-03-US20260068564A1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-20T13:00:00Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>evening-incremental-sprint</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>include_core_epi</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>EPI-INCREMENTAL-SPRINT-evening-2026-10-20-frozen.json</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -28542,27 +28538,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-US20260062803A1</t>
+          <t>2026-03-US20260066234A1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-21T02:07:37Z</t>
+          <t>2026-10-20T12:00:00Z</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>morning-gate3-figures</t>
+          <t>read-ruling-r2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>promote_core_team_read</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gate③ backfill 2 figures</t>
+          <t>由 pending 升格 core 月卡；不计为 Gate③ 独立新发现。</t>
         </is>
       </c>
     </row>
@@ -28574,27 +28570,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-02-US12540400B2</t>
+          <t>2026-03-US20260066234A1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>morning-gate3-figures</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Gate③ backfill 1 figures</t>
         </is>
       </c>
     </row>
@@ -28606,27 +28602,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-02-US20260043170A1</t>
+          <t>2026-03-US20260062803A1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T13:00:00Z</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evening-incremental-sprint</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>include_core_epi</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>EPI-INCREMENTAL-SPRINT-evening-2026-10-20-frozen.json</t>
         </is>
       </c>
     </row>
@@ -28638,27 +28634,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-02-US20260047358A1</t>
+          <t>2026-03-US20260062803A1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>morning-gate3-figures</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Gate③ backfill 2 figures</t>
         </is>
       </c>
     </row>
@@ -28670,7 +28666,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-02-WO2026035639A1</t>
+          <t>2026-02-US12540400B2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -28702,7 +28698,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-02-CN121519154A</t>
+          <t>2026-02-US20260043170A1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -28734,7 +28730,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-02-US12557185B2</t>
+          <t>2026-02-US20260047358A1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -28766,7 +28762,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-02-US20260049767A1</t>
+          <t>2026-02-WO2026035639A1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -28798,7 +28794,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-02-US12564001B2</t>
+          <t>2026-02-CN121519154A</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -28830,7 +28826,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-02-US12543516B2</t>
+          <t>2026-02-US12557185B2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -28862,27 +28858,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-02-US12543516B2</t>
+          <t>2026-02-US20260049767A1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>independent_search_confirm</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>独立检索对照命中。保留基线导入属性，仅记录对照复核。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -28894,7 +28890,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-02-US20260035835A1</t>
+          <t>2026-02-US12564001B2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -28926,27 +28922,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-02-US20260055532A1</t>
+          <t>2026-02-US12543516B2</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -28958,27 +28954,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-02-US20260055532A1</t>
+          <t>2026-02-US12543516B2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-21T02:07:37Z</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>morning-gate3-figures</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>independent_search_confirm</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gate③ backfill 1 figures</t>
+          <t>独立检索对照命中。保留基线导入属性，仅记录对照复核。</t>
         </is>
       </c>
     </row>
@@ -28990,7 +28986,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-01-WO2026024419A1</t>
+          <t>2026-02-US20260035835A1</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -29022,27 +29018,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-01-KR102918757B1</t>
+          <t>2026-02-US20260055532A1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -29054,27 +29050,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-01-WO2026016396A1</t>
+          <t>2026-02-US20260055532A1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>morning-gate3-figures</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Gate③ backfill 1 figures</t>
         </is>
       </c>
     </row>
@@ -29086,7 +29082,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-01-US20260026275A1</t>
+          <t>2026-01-WO2026024419A1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -29118,7 +29114,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-01-KR102915695B1</t>
+          <t>2026-01-KR102918757B1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -29150,27 +29146,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-01-KR102916044B1</t>
+          <t>2026-01-WO2026016396A1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-20T13:00:00Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>evening-incremental-sprint</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>include_core_preclean_family</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>PRECLEAN-INCREMENTAL-SPRINT-evening-2026-10-20-frozen.json</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -29182,27 +29178,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-01-KR102916044B1</t>
+          <t>2026-01-US20260026275A1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-21T02:07:37Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>morning-gate3-figures</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gate③ backfill 6 figures</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -29214,7 +29210,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-01-US20260015766A1</t>
+          <t>2026-01-KR102915695B1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -29246,27 +29242,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-01-US12526971B2</t>
+          <t>2026-01-KR102916044B1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T13:00:00Z</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evening-incremental-sprint</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>include_core_preclean_family</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>PRECLEAN-INCREMENTAL-SPRINT-evening-2026-10-20-frozen.json</t>
         </is>
       </c>
     </row>
@@ -29278,27 +29274,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-01-US12526971B2</t>
+          <t>2026-01-KR102916044B1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>morning-gate3-figures</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>independent_search_confirm</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>独立 EPI 检索再次命中本条（2026-01 授权）。仅作对照确认，仍计为基线导入（imported baseline），不记为本团队新发现。</t>
+          <t>Gate③ backfill 6 figures</t>
         </is>
       </c>
     </row>
@@ -29310,7 +29306,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-01-US20260009155A1</t>
+          <t>2026-01-US20260015766A1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -29342,7 +29338,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-01-WO2026005974A1</t>
+          <t>2026-01-US12526971B2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -29374,27 +29370,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2025-12-KR20250168533A</t>
+          <t>2026-01-US12526971B2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_search_confirm</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立 EPI 检索再次命中本条（2026-01 授权）。仅作对照确认，仍计为基线导入（imported baseline），不记为本团队新发现。</t>
         </is>
       </c>
     </row>
@@ -29406,7 +29402,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2025-12-US20250379096A1</t>
+          <t>2026-01-US20260009155A1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -29438,7 +29434,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2025-12-US20250385089A1</t>
+          <t>2026-01-WO2026005974A1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -29470,7 +29466,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2025-12-US20250385122A1</t>
+          <t>2025-12-KR20250168533A</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -29502,7 +29498,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2025-12-US12503791B2</t>
+          <t>2025-12-US20250379096A1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -29534,7 +29530,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2025-12-KR102904356B1</t>
+          <t>2025-12-US20250385089A1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -29566,7 +29562,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2025-12-WO2025260942A1</t>
+          <t>2025-12-US20250385122A1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -29598,7 +29594,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2025-12-US12512362B2</t>
+          <t>2025-12-US12503791B2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -29630,7 +29626,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2025-12-US20250369154A1</t>
+          <t>2025-12-KR102904356B1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -29662,7 +29658,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2025-11-KR102886069B1</t>
+          <t>2025-12-WO2025260942A1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -29694,7 +29690,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2025-11-US20250351329A1</t>
+          <t>2025-12-US12512362B2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -29726,7 +29722,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2025-11-WO2025232199A1</t>
+          <t>2025-12-US20250369154A1</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -29758,7 +29754,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2025-11-TW202544883A</t>
+          <t>2025-11-KR102886069B1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -29790,7 +29786,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2025-11-KR102888301B1</t>
+          <t>2025-11-US20250351329A1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -29822,7 +29818,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2025-11-US20250358906A1</t>
+          <t>2025-11-WO2025232199A1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -29854,7 +29850,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2025-11-CN120989593A</t>
+          <t>2025-11-TW202544883A</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -29886,7 +29882,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2025-11-CN121002222A</t>
+          <t>2025-11-KR102888301B1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -29918,7 +29914,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2025-11-CN121002231A</t>
+          <t>2025-11-US20250358906A1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -29950,7 +29946,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2025-11-CN121002616A</t>
+          <t>2025-11-CN120989593A</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -29982,7 +29978,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2025-11-CN121002621A</t>
+          <t>2025-11-CN121002222A</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -30014,7 +30010,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2025-11-KR102889785B1</t>
+          <t>2025-11-CN121002231A</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -30046,7 +30042,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2025-11-TWI905596B</t>
+          <t>2025-11-CN121002616A</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -30078,7 +30074,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2025-11-CN223598701U</t>
+          <t>2025-11-CN121002621A</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -30110,7 +30106,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2025-11-US12480223B2</t>
+          <t>2025-11-KR102889785B1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -30142,7 +30138,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2025-11-US12482662B2</t>
+          <t>2025-11-TWI905596B</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -30174,7 +30170,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2025-11-US12484327B2</t>
+          <t>2025-11-CN223598701U</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -30206,7 +30202,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2025-11-JP7776424B2</t>
+          <t>2025-11-US12480223B2</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -30238,7 +30234,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2025-11-DE112021001213B4</t>
+          <t>2025-11-US12482662B2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -30270,7 +30266,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2025-11-WO2025244833A1</t>
+          <t>2025-11-US12484327B2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -30302,7 +30298,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2025-10-WO2025225316A1</t>
+          <t>2025-11-JP7776424B2</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -30334,7 +30330,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2025-10-WO2025222891A1</t>
+          <t>2025-11-DE112021001213B4</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -30366,7 +30362,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2025-10-US12454769B2</t>
+          <t>2025-11-WO2025244833A1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -30398,7 +30394,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2025-10-US20250327211A1</t>
+          <t>2025-10-WO2025225316A1</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -30430,7 +30426,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2025-10-WO2025220436A1</t>
+          <t>2025-10-WO2025222891A1</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -30462,7 +30458,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2025-10-WO2025221932A1</t>
+          <t>2025-10-US12454769B2</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -30494,7 +30490,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2025-10-US20250331222A1</t>
+          <t>2025-10-US20250327211A1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -30526,27 +30522,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2025-10-US20250327209A1</t>
+          <t>2025-10-WO2025220436A1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-10-20T09:31:48Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>evidence-review-r2</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>independent_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>独立检索新纳入（非基线导入）。</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -30558,27 +30554,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2025-10-US20250327209A1</t>
+          <t>2025-10-WO2025221932A1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-10-21T02:07:37Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>morning-gate3-figures</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>attach_gate3_family_figures</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gate③ backfill 1 figures</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30586,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2025-10-JP7757917B2</t>
+          <t>2025-10-US20250331222A1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -30622,27 +30618,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2025-10-KR20250150601A</t>
+          <t>2025-10-US20250327209A1</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-20T09:31:48Z</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>evidence-review-r2</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>independent_add</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>独立检索新纳入（非基线导入）。</t>
         </is>
       </c>
     </row>
@@ -30654,27 +30650,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2025-10-CN120797198A</t>
+          <t>2025-10-US20250327209A1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-10-20T17:30:00+08:00</t>
+          <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>baseline-import</t>
+          <t>morning-gate3-figures</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>attach_gate3_family_figures</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+          <t>Gate③ backfill 1 figures</t>
         </is>
       </c>
     </row>
@@ -30686,7 +30682,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2025-10-US20250324699A1</t>
+          <t>2025-10-JP7757917B2</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -30718,7 +30714,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2025-10-US12444605B2</t>
+          <t>2025-10-KR20250150601A</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -30750,7 +30746,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2025-10-KR102870814B1</t>
+          <t>2025-10-CN120797198A</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -30782,7 +30778,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2025-10-WO2025211045A1</t>
+          <t>2025-10-US20250324699A1</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -30814,7 +30810,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2025-10-JP2025533523A</t>
+          <t>2025-10-US12444605B2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -30846,7 +30842,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2025-10-WO2025204274A1</t>
+          <t>2025-10-KR102870814B1</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -30878,27 +30874,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2025-10-US20250311241A1</t>
+          <t>2025-10-WO2025211045A1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-20T10:37:42Z</t>
+          <t>2026-10-20T17:30:00+08:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>sprint-gap-a</t>
+          <t>baseline-import</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>content_add</t>
+          <t>import</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
         </is>
       </c>
     </row>
@@ -30910,25 +30906,121 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>2025-10-JP2025533523A</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-10-20T17:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>baseline-import</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2025-10-WO2025204274A1</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-10-20T17:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>baseline-import</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Imported from Dot reference report; not this team's independent discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
           <t>2025-10-US20250311241A1</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-10-20T10:37:42Z</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>sprint-gap-a</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>content_add</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>EVIDENCE-SPRINT-A / EPI-INCREMENTAL-SPRINT-gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2025-10-US20250311241A1</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
         <is>
           <t>2026-10-21T02:07:37Z</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>morning-gate3-figures</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E170" t="inlineStr">
         <is>
           <t>attach_gate3_family_figures</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>Gate③ backfill 1 figures</t>
         </is>
